--- a/static/sample-data/planning/synth_fmcg_brand.xlsx
+++ b/static/sample-data/planning/synth_fmcg_brand.xlsx
@@ -388,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -437,7 +437,7 @@
         <v>44928</v>
       </c>
       <c r="B2">
-        <v>107980567</v>
+        <v>249742423</v>
       </c>
       <c r="C2">
         <v>19835353</v>
@@ -446,10 +446,10 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E2">
-        <v>7012448</v>
+        <v>16320988</v>
       </c>
       <c r="F2">
-        <v>36211620</v>
+        <v>84280044</v>
       </c>
       <c r="G2">
         <v>5695388</v>
@@ -458,10 +458,10 @@
         <v>69537599</v>
       </c>
       <c r="I2">
-        <v>2759513</v>
+        <v>8828631</v>
       </c>
       <c r="J2">
-        <v>61543</v>
+        <v>196896</v>
       </c>
       <c r="K2">
         <v>40.4</v>
@@ -470,7 +470,7 @@
         <v>1.041</v>
       </c>
       <c r="M2">
-        <v>577121855</v>
+        <v>1093266021</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -478,7 +478,7 @@
         <v>44935</v>
       </c>
       <c r="B3">
-        <v>111891058</v>
+        <v>239463473</v>
       </c>
       <c r="C3">
         <v>8673436</v>
@@ -487,10 +487,10 @@
         <v>32.3</v>
       </c>
       <c r="E3">
-        <v>3982849</v>
+        <v>9477627</v>
       </c>
       <c r="F3">
-        <v>19114760</v>
+        <v>45485676</v>
       </c>
       <c r="G3">
         <v>3625723</v>
@@ -499,10 +499,10 @@
         <v>44889625</v>
       </c>
       <c r="I3">
-        <v>1469407</v>
+        <v>4692311</v>
       </c>
       <c r="J3">
-        <v>32162</v>
+        <v>102704</v>
       </c>
       <c r="K3">
         <v>58.4</v>
@@ -511,7 +511,7 @@
         <v>0.9550999999999999</v>
       </c>
       <c r="M3">
-        <v>556472310</v>
+        <v>1054148725</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -519,7 +519,7 @@
         <v>44942</v>
       </c>
       <c r="B4">
-        <v>117428289</v>
+        <v>241418046</v>
       </c>
       <c r="C4">
         <v>8810814</v>
@@ -528,10 +528,10 @@
         <v>36.7</v>
       </c>
       <c r="E4">
-        <v>4634348</v>
+        <v>11369765</v>
       </c>
       <c r="F4">
-        <v>22864994</v>
+        <v>56096261</v>
       </c>
       <c r="G4">
         <v>9187818</v>
@@ -540,10 +540,10 @@
         <v>112883164</v>
       </c>
       <c r="I4">
-        <v>1297676</v>
+        <v>4329142</v>
       </c>
       <c r="J4">
-        <v>28987</v>
+        <v>96702</v>
       </c>
       <c r="K4">
         <v>101.5</v>
@@ -552,7 +552,7 @@
         <v>0.9636</v>
       </c>
       <c r="M4">
-        <v>586525294</v>
+        <v>1111079349</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -560,7 +560,7 @@
         <v>44949</v>
       </c>
       <c r="B5">
-        <v>126100781</v>
+        <v>246214621</v>
       </c>
       <c r="C5">
         <v>8095567</v>
@@ -569,10 +569,10 @@
         <v>32.7</v>
       </c>
       <c r="E5">
-        <v>8550229</v>
+        <v>20157810</v>
       </c>
       <c r="F5">
-        <v>42247022</v>
+        <v>99600548</v>
       </c>
       <c r="G5">
         <v>6908127</v>
@@ -581,10 +581,10 @@
         <v>83284812</v>
       </c>
       <c r="I5">
-        <v>1075046</v>
+        <v>3589733</v>
       </c>
       <c r="J5">
-        <v>24171</v>
+        <v>80710</v>
       </c>
       <c r="K5">
         <v>143.8</v>
@@ -593,7 +593,7 @@
         <v>0.9635</v>
       </c>
       <c r="M5">
-        <v>555438524</v>
+        <v>1052190382</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -601,7 +601,7 @@
         <v>44956</v>
       </c>
       <c r="B6">
-        <v>129554399</v>
+        <v>244545371</v>
       </c>
       <c r="C6">
         <v>4535028</v>
@@ -610,10 +610,10 @@
         <v>18.1</v>
       </c>
       <c r="E6">
-        <v>8008075</v>
+        <v>18385914</v>
       </c>
       <c r="F6">
-        <v>41846903</v>
+        <v>96077210</v>
       </c>
       <c r="G6">
         <v>4019196</v>
@@ -622,10 +622,10 @@
         <v>49672684</v>
       </c>
       <c r="I6">
-        <v>1132013</v>
+        <v>3813972</v>
       </c>
       <c r="J6">
-        <v>23972</v>
+        <v>80765</v>
       </c>
       <c r="K6">
         <v>162.4</v>
@@ -634,7 +634,7 @@
         <v>0.979</v>
       </c>
       <c r="M6">
-        <v>595489039</v>
+        <v>1128059745</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -642,7 +642,7 @@
         <v>44963</v>
       </c>
       <c r="B7">
-        <v>117119603</v>
+        <v>221034146</v>
       </c>
       <c r="C7">
         <v>12299505</v>
@@ -651,10 +651,10 @@
         <v>49.8</v>
       </c>
       <c r="E7">
-        <v>67638</v>
+        <v>163177</v>
       </c>
       <c r="F7">
-        <v>324507</v>
+        <v>782878</v>
       </c>
       <c r="G7">
         <v>11608408</v>
@@ -663,10 +663,10 @@
         <v>148830434</v>
       </c>
       <c r="I7">
-        <v>1165462</v>
+        <v>3791524</v>
       </c>
       <c r="J7">
-        <v>27115</v>
+        <v>88213</v>
       </c>
       <c r="K7">
         <v>38.3</v>
@@ -675,7 +675,7 @@
         <v>1.0731</v>
       </c>
       <c r="M7">
-        <v>543926402</v>
+        <v>1030382490</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -683,7 +683,7 @@
         <v>44970</v>
       </c>
       <c r="B8">
-        <v>134539157</v>
+        <v>252178846</v>
       </c>
       <c r="C8">
         <v>8413387</v>
@@ -692,10 +692,10 @@
         <v>33.9</v>
       </c>
       <c r="E8">
-        <v>11440060</v>
+        <v>26359261</v>
       </c>
       <c r="F8">
-        <v>57723313</v>
+        <v>133001391</v>
       </c>
       <c r="G8">
         <v>7150813</v>
@@ -704,10 +704,10 @@
         <v>94554933</v>
       </c>
       <c r="I8">
-        <v>1473383</v>
+        <v>4792080</v>
       </c>
       <c r="J8">
-        <v>30752</v>
+        <v>100020</v>
       </c>
       <c r="K8">
         <v>78.2</v>
@@ -716,7 +716,7 @@
         <v>0.9877</v>
       </c>
       <c r="M8">
-        <v>576691369</v>
+        <v>1092450533</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -724,7 +724,7 @@
         <v>44977</v>
       </c>
       <c r="B9">
-        <v>130252475</v>
+        <v>248670956</v>
       </c>
       <c r="C9">
         <v>7396471</v>
@@ -733,10 +733,10 @@
         <v>30.4</v>
       </c>
       <c r="E9">
-        <v>3467846</v>
+        <v>8935921</v>
       </c>
       <c r="F9">
-        <v>17422340</v>
+        <v>44893761</v>
       </c>
       <c r="G9">
         <v>11117526</v>
@@ -745,10 +745,10 @@
         <v>131586257</v>
       </c>
       <c r="I9">
-        <v>2059635</v>
+        <v>6584825</v>
       </c>
       <c r="J9">
-        <v>47046</v>
+        <v>150410</v>
       </c>
       <c r="K9">
         <v>94.8</v>
@@ -757,7 +757,7 @@
         <v>1.0097</v>
       </c>
       <c r="M9">
-        <v>529821348</v>
+        <v>1003662697</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -765,7 +765,7 @@
         <v>44984</v>
       </c>
       <c r="B10">
-        <v>129263850</v>
+        <v>234903093</v>
       </c>
       <c r="C10">
         <v>7805853</v>
@@ -774,10 +774,10 @@
         <v>31.1</v>
       </c>
       <c r="E10">
-        <v>7931874</v>
+        <v>18246311</v>
       </c>
       <c r="F10">
-        <v>42471434</v>
+        <v>97700362</v>
       </c>
       <c r="G10">
         <v>3325820</v>
@@ -786,10 +786,10 @@
         <v>42536909</v>
       </c>
       <c r="I10">
-        <v>670750</v>
+        <v>2251751</v>
       </c>
       <c r="J10">
-        <v>14813</v>
+        <v>49729</v>
       </c>
       <c r="K10">
         <v>156.6</v>
@@ -798,7 +798,7 @@
         <v>1.0045</v>
       </c>
       <c r="M10">
-        <v>555653236</v>
+        <v>1052597120</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -806,7 +806,7 @@
         <v>44991</v>
       </c>
       <c r="B11">
-        <v>122306946</v>
+        <v>231808448</v>
       </c>
       <c r="C11">
         <v>16683665</v>
@@ -815,10 +815,10 @@
         <v>63.9</v>
       </c>
       <c r="E11">
-        <v>3098746</v>
+        <v>7447749</v>
       </c>
       <c r="F11">
-        <v>14599800</v>
+        <v>35090214</v>
       </c>
       <c r="G11">
         <v>4744374</v>
@@ -827,10 +827,10 @@
         <v>56536868</v>
       </c>
       <c r="I11">
-        <v>1399011</v>
+        <v>4722316</v>
       </c>
       <c r="J11">
-        <v>30578</v>
+        <v>103215</v>
       </c>
       <c r="K11">
         <v>142.6</v>
@@ -839,7 +839,7 @@
         <v>0.9734</v>
       </c>
       <c r="M11">
-        <v>544489934</v>
+        <v>1031450012</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -847,7 +847,7 @@
         <v>44998</v>
       </c>
       <c r="B12">
-        <v>126022158</v>
+        <v>242867446</v>
       </c>
       <c r="C12">
         <v>7794059</v>
@@ -856,10 +856,10 @@
         <v>28.9</v>
       </c>
       <c r="E12">
-        <v>5692843</v>
+        <v>13916712</v>
       </c>
       <c r="F12">
-        <v>26687422</v>
+        <v>65240022</v>
       </c>
       <c r="G12">
         <v>5538838</v>
@@ -868,10 +868,10 @@
         <v>73168634</v>
       </c>
       <c r="I12">
-        <v>1998910</v>
+        <v>6644445</v>
       </c>
       <c r="J12">
-        <v>43572</v>
+        <v>144835</v>
       </c>
       <c r="K12">
         <v>49.9</v>
@@ -880,7 +880,7 @@
         <v>1.0051</v>
       </c>
       <c r="M12">
-        <v>587638509</v>
+        <v>1113188159</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -888,7 +888,7 @@
         <v>45005</v>
       </c>
       <c r="B13">
-        <v>132040873</v>
+        <v>247913468</v>
       </c>
       <c r="C13">
         <v>13083010</v>
@@ -897,10 +897,10 @@
         <v>51.2</v>
       </c>
       <c r="E13">
-        <v>5961552</v>
+        <v>13897914</v>
       </c>
       <c r="F13">
-        <v>30103894</v>
+        <v>70179931</v>
       </c>
       <c r="G13">
         <v>5553865</v>
@@ -909,10 +909,10 @@
         <v>70953161</v>
       </c>
       <c r="I13">
-        <v>2549205</v>
+        <v>8222227</v>
       </c>
       <c r="J13">
-        <v>58803</v>
+        <v>189663</v>
       </c>
       <c r="K13">
         <v>116.4</v>
@@ -921,7 +921,7 @@
         <v>1.0132</v>
       </c>
       <c r="M13">
-        <v>543234873</v>
+        <v>1029072496</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -929,7 +929,7 @@
         <v>45012</v>
       </c>
       <c r="B14">
-        <v>115592035</v>
+        <v>209596299</v>
       </c>
       <c r="C14">
         <v>83790</v>
@@ -938,10 +938,10 @@
         <v>0.3</v>
       </c>
       <c r="E14">
-        <v>85279</v>
+        <v>196207</v>
       </c>
       <c r="F14">
-        <v>430895</v>
+        <v>991388</v>
       </c>
       <c r="G14">
         <v>4487807</v>
@@ -950,10 +950,10 @@
         <v>56484121</v>
       </c>
       <c r="I14">
-        <v>1684524</v>
+        <v>5455421</v>
       </c>
       <c r="J14">
-        <v>37412</v>
+        <v>121161</v>
       </c>
       <c r="K14">
         <v>38.8</v>
@@ -962,7 +962,7 @@
         <v>0.9683</v>
       </c>
       <c r="M14">
-        <v>521244753</v>
+        <v>987415694</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -970,7 +970,7 @@
         <v>45019</v>
       </c>
       <c r="B15">
-        <v>116804144</v>
+        <v>220479650</v>
       </c>
       <c r="C15">
         <v>78160</v>
@@ -979,10 +979,10 @@
         <v>0.3</v>
       </c>
       <c r="E15">
-        <v>6455990</v>
+        <v>14813583</v>
       </c>
       <c r="F15">
-        <v>31192497</v>
+        <v>71572697</v>
       </c>
       <c r="G15">
         <v>9732975</v>
@@ -991,10 +991,10 @@
         <v>120862907</v>
       </c>
       <c r="I15">
-        <v>1384016</v>
+        <v>4546426</v>
       </c>
       <c r="J15">
-        <v>29341</v>
+        <v>96383</v>
       </c>
       <c r="K15">
         <v>67.8</v>
@@ -1003,7 +1003,7 @@
         <v>1.0592</v>
       </c>
       <c r="M15">
-        <v>518936781</v>
+        <v>983043606</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1011,7 +1011,7 @@
         <v>45026</v>
       </c>
       <c r="B16">
-        <v>115567731</v>
+        <v>217561313</v>
       </c>
       <c r="C16">
         <v>256065</v>
@@ -1020,10 +1020,10 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>4977484</v>
+        <v>11941492</v>
       </c>
       <c r="F16">
-        <v>24305877</v>
+        <v>58312274</v>
       </c>
       <c r="G16">
         <v>4537245</v>
@@ -1032,10 +1032,10 @@
         <v>56505124</v>
       </c>
       <c r="I16">
-        <v>1581470</v>
+        <v>5179469</v>
       </c>
       <c r="J16">
-        <v>33591</v>
+        <v>110014</v>
       </c>
       <c r="K16">
         <v>56.2</v>
@@ -1044,7 +1044,7 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="M16">
-        <v>524380290</v>
+        <v>993355473</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1052,7 +1052,7 @@
         <v>45033</v>
       </c>
       <c r="B17">
-        <v>115544494</v>
+        <v>220391519</v>
       </c>
       <c r="C17">
         <v>8949495</v>
@@ -1061,10 +1061,10 @@
         <v>35.3</v>
       </c>
       <c r="E17">
-        <v>6424276</v>
+        <v>15310083</v>
       </c>
       <c r="F17">
-        <v>32381485</v>
+        <v>77170289</v>
       </c>
       <c r="G17">
         <v>4298763</v>
@@ -1073,10 +1073,10 @@
         <v>48890155</v>
       </c>
       <c r="I17">
-        <v>1281314</v>
+        <v>4396769</v>
       </c>
       <c r="J17">
-        <v>27538</v>
+        <v>94497</v>
       </c>
       <c r="K17">
         <v>156.7</v>
@@ -1085,7 +1085,7 @@
         <v>1.0379</v>
       </c>
       <c r="M17">
-        <v>514577691</v>
+        <v>974786001</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1093,7 +1093,7 @@
         <v>45040</v>
       </c>
       <c r="B18">
-        <v>116846249</v>
+        <v>223266775</v>
       </c>
       <c r="C18">
         <v>5886228</v>
@@ -1102,10 +1102,10 @@
         <v>23.1</v>
       </c>
       <c r="E18">
-        <v>5972628</v>
+        <v>14278919</v>
       </c>
       <c r="F18">
-        <v>30234931</v>
+        <v>72283449</v>
       </c>
       <c r="G18">
         <v>8151562</v>
@@ -1114,10 +1114,10 @@
         <v>98223568</v>
       </c>
       <c r="I18">
-        <v>1383760</v>
+        <v>4661898</v>
       </c>
       <c r="J18">
-        <v>31913</v>
+        <v>107516</v>
       </c>
       <c r="K18">
         <v>41.3</v>
@@ -1126,7 +1126,7 @@
         <v>1.0385</v>
       </c>
       <c r="M18">
-        <v>496909192</v>
+        <v>941315826</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1134,7 +1134,7 @@
         <v>45047</v>
       </c>
       <c r="B19">
-        <v>108285055</v>
+        <v>207792469</v>
       </c>
       <c r="C19">
         <v>5775638</v>
@@ -1143,10 +1143,10 @@
         <v>23.4</v>
       </c>
       <c r="E19">
-        <v>2785221</v>
+        <v>7072513</v>
       </c>
       <c r="F19">
-        <v>13289809</v>
+        <v>33746819</v>
       </c>
       <c r="G19">
         <v>9304061</v>
@@ -1155,10 +1155,10 @@
         <v>113475718</v>
       </c>
       <c r="I19">
-        <v>1336212</v>
+        <v>4347282</v>
       </c>
       <c r="J19">
-        <v>29957</v>
+        <v>97462</v>
       </c>
       <c r="K19">
         <v>132.6</v>
@@ -1167,7 +1167,7 @@
         <v>0.9785</v>
       </c>
       <c r="M19">
-        <v>495371404</v>
+        <v>938402729</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1175,7 +1175,7 @@
         <v>45054</v>
       </c>
       <c r="B20">
-        <v>116864218</v>
+        <v>222541204</v>
       </c>
       <c r="C20">
         <v>3728686</v>
@@ -1184,10 +1184,10 @@
         <v>15.2</v>
       </c>
       <c r="E20">
-        <v>4556905</v>
+        <v>11134736</v>
       </c>
       <c r="F20">
-        <v>22397485</v>
+        <v>54727959</v>
       </c>
       <c r="G20">
         <v>10076570</v>
@@ -1196,10 +1196,10 @@
         <v>124640744</v>
       </c>
       <c r="I20">
-        <v>3098972</v>
+        <v>9884359</v>
       </c>
       <c r="J20">
-        <v>66862</v>
+        <v>213261</v>
       </c>
       <c r="K20">
         <v>107.5</v>
@@ -1208,7 +1208,7 @@
         <v>0.9817</v>
       </c>
       <c r="M20">
-        <v>480100569</v>
+        <v>909474550</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1216,7 +1216,7 @@
         <v>45061</v>
       </c>
       <c r="B21">
-        <v>106962769</v>
+        <v>203437406</v>
       </c>
       <c r="C21">
         <v>7275452</v>
@@ -1225,10 +1225,10 @@
         <v>28.5</v>
       </c>
       <c r="E21">
-        <v>4154215</v>
+        <v>10243049</v>
       </c>
       <c r="F21">
-        <v>20508113</v>
+        <v>50566867</v>
       </c>
       <c r="G21">
         <v>15604253</v>
@@ -1237,10 +1237,10 @@
         <v>197697755</v>
       </c>
       <c r="I21">
-        <v>872718</v>
+        <v>2904998</v>
       </c>
       <c r="J21">
-        <v>18278</v>
+        <v>60842</v>
       </c>
       <c r="K21">
         <v>172.9</v>
@@ -1249,7 +1249,7 @@
         <v>0.9639</v>
       </c>
       <c r="M21">
-        <v>486802059</v>
+        <v>922169461</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1257,7 +1257,7 @@
         <v>45068</v>
       </c>
       <c r="B22">
-        <v>104167958</v>
+        <v>185129724</v>
       </c>
       <c r="C22">
         <v>14131510</v>
@@ -1266,10 +1266,10 @@
         <v>56</v>
       </c>
       <c r="E22">
-        <v>6233260</v>
+        <v>14641969</v>
       </c>
       <c r="F22">
-        <v>30804983</v>
+        <v>72361105</v>
       </c>
       <c r="G22">
         <v>206906</v>
@@ -1278,10 +1278,10 @@
         <v>2537833</v>
       </c>
       <c r="I22">
-        <v>46135</v>
+        <v>149015</v>
       </c>
       <c r="J22">
-        <v>968</v>
+        <v>3126</v>
       </c>
       <c r="K22">
         <v>178.1</v>
@@ -1290,7 +1290,7 @@
         <v>1.036</v>
       </c>
       <c r="M22">
-        <v>452033135</v>
+        <v>856305237</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1298,7 +1298,7 @@
         <v>45075</v>
       </c>
       <c r="B23">
-        <v>107329706</v>
+        <v>210188293</v>
       </c>
       <c r="C23">
         <v>11544160</v>
@@ -1307,10 +1307,10 @@
         <v>44.9</v>
       </c>
       <c r="E23">
-        <v>3956870</v>
+        <v>9488940</v>
       </c>
       <c r="F23">
-        <v>19352816</v>
+        <v>46409846</v>
       </c>
       <c r="G23">
         <v>229551</v>
@@ -1319,10 +1319,10 @@
         <v>2806414</v>
       </c>
       <c r="I23">
-        <v>1989342</v>
+        <v>6344208</v>
       </c>
       <c r="J23">
-        <v>46557</v>
+        <v>148475</v>
       </c>
       <c r="K23">
         <v>75.40000000000001</v>
@@ -1331,7 +1331,7 @@
         <v>1.0759</v>
       </c>
       <c r="M23">
-        <v>469101842</v>
+        <v>888639202</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1339,7 +1339,7 @@
         <v>45082</v>
       </c>
       <c r="B24">
-        <v>120497328</v>
+        <v>227462722</v>
       </c>
       <c r="C24">
         <v>12018919</v>
@@ -1348,10 +1348,10 @@
         <v>47.7</v>
       </c>
       <c r="E24">
-        <v>9324961</v>
+        <v>21572077</v>
       </c>
       <c r="F24">
-        <v>46042234</v>
+        <v>106512680</v>
       </c>
       <c r="G24">
         <v>11047991</v>
@@ -1360,10 +1360,10 @@
         <v>141147038</v>
       </c>
       <c r="I24">
-        <v>2067332</v>
+        <v>6786230</v>
       </c>
       <c r="J24">
-        <v>43744</v>
+        <v>143594</v>
       </c>
       <c r="K24">
         <v>145.6</v>
@@ -1372,7 +1372,7 @@
         <v>0.948</v>
       </c>
       <c r="M24">
-        <v>424993894</v>
+        <v>805083674</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1380,7 +1380,7 @@
         <v>45089</v>
       </c>
       <c r="B25">
-        <v>120693107</v>
+        <v>223351756</v>
       </c>
       <c r="C25">
         <v>163200</v>
@@ -1389,10 +1389,10 @@
         <v>0.6</v>
       </c>
       <c r="E25">
-        <v>5776523</v>
+        <v>13445667</v>
       </c>
       <c r="F25">
-        <v>29525116</v>
+        <v>68723851</v>
       </c>
       <c r="G25">
         <v>4485068</v>
@@ -1401,10 +1401,10 @@
         <v>55210518</v>
       </c>
       <c r="I25">
-        <v>2279843</v>
+        <v>7414294</v>
       </c>
       <c r="J25">
-        <v>48338</v>
+        <v>157199</v>
       </c>
       <c r="K25">
         <v>25.7</v>
@@ -1413,7 +1413,7 @@
         <v>1.014</v>
       </c>
       <c r="M25">
-        <v>463311037</v>
+        <v>877669437</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1421,7 +1421,7 @@
         <v>45096</v>
       </c>
       <c r="B26">
-        <v>118692267</v>
+        <v>215546992</v>
       </c>
       <c r="C26">
         <v>12030193</v>
@@ -1430,10 +1430,10 @@
         <v>46.3</v>
       </c>
       <c r="E26">
-        <v>2436589</v>
+        <v>6446562</v>
       </c>
       <c r="F26">
-        <v>11648262</v>
+        <v>30818181</v>
       </c>
       <c r="G26">
         <v>10884638</v>
@@ -1442,10 +1442,10 @@
         <v>133939746</v>
       </c>
       <c r="I26">
-        <v>3268333</v>
+        <v>10413579</v>
       </c>
       <c r="J26">
-        <v>71177</v>
+        <v>226783</v>
       </c>
       <c r="K26">
         <v>126.9</v>
@@ -1454,7 +1454,7 @@
         <v>1.0316</v>
       </c>
       <c r="M26">
-        <v>466886176</v>
+        <v>884441973</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1462,7 +1462,7 @@
         <v>45103</v>
       </c>
       <c r="B27">
-        <v>117160778</v>
+        <v>216785411</v>
       </c>
       <c r="C27">
         <v>10482197</v>
@@ -1471,10 +1471,10 @@
         <v>39.6</v>
       </c>
       <c r="E27">
-        <v>6608846</v>
+        <v>15177227</v>
       </c>
       <c r="F27">
-        <v>32402967</v>
+        <v>74413473</v>
       </c>
       <c r="G27">
         <v>10177892</v>
@@ -1483,10 +1483,10 @@
         <v>123611512</v>
       </c>
       <c r="I27">
-        <v>1699681</v>
+        <v>5419511</v>
       </c>
       <c r="J27">
-        <v>35303</v>
+        <v>112564</v>
       </c>
       <c r="K27">
         <v>65.3</v>
@@ -1495,7 +1495,7 @@
         <v>1.0437</v>
       </c>
       <c r="M27">
-        <v>472842664</v>
+        <v>895725598</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1503,7 +1503,7 @@
         <v>45110</v>
       </c>
       <c r="B28">
-        <v>114768929</v>
+        <v>214048508</v>
       </c>
       <c r="C28">
         <v>7572540</v>
@@ -1512,10 +1512,10 @@
         <v>30.2</v>
       </c>
       <c r="E28">
-        <v>5429088</v>
+        <v>12575765</v>
       </c>
       <c r="F28">
-        <v>26623135</v>
+        <v>61668977</v>
       </c>
       <c r="G28">
         <v>5695646</v>
@@ -1524,10 +1524,10 @@
         <v>68299402</v>
       </c>
       <c r="I28">
-        <v>1794883</v>
+        <v>5821912</v>
       </c>
       <c r="J28">
-        <v>37519</v>
+        <v>121697</v>
       </c>
       <c r="K28">
         <v>29.9</v>
@@ -1536,7 +1536,7 @@
         <v>1.0146</v>
       </c>
       <c r="M28">
-        <v>471158176</v>
+        <v>892534601</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1544,7 +1544,7 @@
         <v>45117</v>
       </c>
       <c r="B29">
-        <v>115652460</v>
+        <v>214305455</v>
       </c>
       <c r="C29">
         <v>10706053</v>
@@ -1553,10 +1553,10 @@
         <v>39.6</v>
       </c>
       <c r="E29">
-        <v>3782767</v>
+        <v>9208892</v>
       </c>
       <c r="F29">
-        <v>19354477</v>
+        <v>47117179</v>
       </c>
       <c r="G29">
         <v>3764589</v>
@@ -1565,10 +1565,10 @@
         <v>45555147</v>
       </c>
       <c r="I29">
-        <v>2984182</v>
+        <v>9666418</v>
       </c>
       <c r="J29">
-        <v>63626</v>
+        <v>206097</v>
       </c>
       <c r="K29">
         <v>173.5</v>
@@ -1577,7 +1577,7 @@
         <v>0.9978</v>
       </c>
       <c r="M29">
-        <v>460004787</v>
+        <v>871406271</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1585,7 +1585,7 @@
         <v>45124</v>
       </c>
       <c r="B30">
-        <v>108057666</v>
+        <v>201364474</v>
       </c>
       <c r="C30">
         <v>18249270</v>
@@ -1594,10 +1594,10 @@
         <v>68.8</v>
       </c>
       <c r="E30">
-        <v>4551236</v>
+        <v>10878786</v>
       </c>
       <c r="F30">
-        <v>22562123</v>
+        <v>53930083</v>
       </c>
       <c r="G30">
         <v>5528233</v>
@@ -1606,10 +1606,10 @@
         <v>68817024</v>
       </c>
       <c r="I30">
-        <v>744601</v>
+        <v>2586625</v>
       </c>
       <c r="J30">
-        <v>16610</v>
+        <v>57700</v>
       </c>
       <c r="K30">
         <v>46.2</v>
@@ -1618,7 +1618,7 @@
         <v>0.9726</v>
       </c>
       <c r="M30">
-        <v>450004613</v>
+        <v>852462523</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1626,7 +1626,7 @@
         <v>45131</v>
       </c>
       <c r="B31">
-        <v>104460728</v>
+        <v>198271626</v>
       </c>
       <c r="C31">
         <v>6506709</v>
@@ -1635,10 +1635,10 @@
         <v>25.4</v>
       </c>
       <c r="E31">
-        <v>3230505</v>
+        <v>7412763</v>
       </c>
       <c r="F31">
-        <v>15442104</v>
+        <v>35433676</v>
       </c>
       <c r="G31">
         <v>11045835</v>
@@ -1647,10 +1647,10 @@
         <v>140750395</v>
       </c>
       <c r="I31">
-        <v>1513924</v>
+        <v>4847202</v>
       </c>
       <c r="J31">
-        <v>32013</v>
+        <v>102498</v>
       </c>
       <c r="K31">
         <v>48.8</v>
@@ -1659,7 +1659,7 @@
         <v>0.9979</v>
       </c>
       <c r="M31">
-        <v>474474993</v>
+        <v>898817787</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1667,7 +1667,7 @@
         <v>45138</v>
       </c>
       <c r="B32">
-        <v>98746175</v>
+        <v>190065414</v>
       </c>
       <c r="C32">
         <v>9574896</v>
@@ -1676,10 +1676,10 @@
         <v>37.7</v>
       </c>
       <c r="E32">
-        <v>3010719</v>
+        <v>7416782</v>
       </c>
       <c r="F32">
-        <v>13711109</v>
+        <v>33776750</v>
       </c>
       <c r="G32">
         <v>4962292</v>
@@ -1688,10 +1688,10 @@
         <v>60766535</v>
       </c>
       <c r="I32">
-        <v>1477047</v>
+        <v>4975469</v>
       </c>
       <c r="J32">
-        <v>30992</v>
+        <v>104397</v>
       </c>
       <c r="K32">
         <v>280.1</v>
@@ -1700,7 +1700,7 @@
         <v>1.0149</v>
       </c>
       <c r="M32">
-        <v>430040126</v>
+        <v>814642963</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1708,7 +1708,7 @@
         <v>45145</v>
       </c>
       <c r="B33">
-        <v>101012858</v>
+        <v>194561535</v>
       </c>
       <c r="C33">
         <v>19271258</v>
@@ -1717,10 +1717,10 @@
         <v>77</v>
       </c>
       <c r="E33">
-        <v>3778992</v>
+        <v>9392795</v>
       </c>
       <c r="F33">
-        <v>18838688</v>
+        <v>46824113</v>
       </c>
       <c r="G33">
         <v>4722841</v>
@@ -1729,10 +1729,10 @@
         <v>55375055</v>
       </c>
       <c r="I33">
-        <v>920557</v>
+        <v>3064324</v>
       </c>
       <c r="J33">
-        <v>20569</v>
+        <v>68470</v>
       </c>
       <c r="K33">
         <v>20.8</v>
@@ -1741,7 +1741,7 @@
         <v>0.9989</v>
       </c>
       <c r="M33">
-        <v>446613099</v>
+        <v>846037837</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1749,7 +1749,7 @@
         <v>45152</v>
       </c>
       <c r="B34">
-        <v>108132175</v>
+        <v>205757192</v>
       </c>
       <c r="C34">
         <v>15743813</v>
@@ -1758,10 +1758,10 @@
         <v>60.1</v>
       </c>
       <c r="E34">
-        <v>6981095</v>
+        <v>16501199</v>
       </c>
       <c r="F34">
-        <v>34124570</v>
+        <v>80660170</v>
       </c>
       <c r="G34">
         <v>7888405</v>
@@ -1770,10 +1770,10 @@
         <v>100573993</v>
       </c>
       <c r="I34">
-        <v>850139</v>
+        <v>2872752</v>
       </c>
       <c r="J34">
-        <v>18497</v>
+        <v>62504</v>
       </c>
       <c r="K34">
         <v>28.8</v>
@@ -1782,7 +1782,7 @@
         <v>1.0112</v>
       </c>
       <c r="M34">
-        <v>481904548</v>
+        <v>912891902</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1790,7 +1790,7 @@
         <v>45159</v>
       </c>
       <c r="B35">
-        <v>112031393</v>
+        <v>216975198</v>
       </c>
       <c r="C35">
         <v>13556199</v>
@@ -1799,10 +1799,10 @@
         <v>53.3</v>
       </c>
       <c r="E35">
-        <v>6516374</v>
+        <v>15776132</v>
       </c>
       <c r="F35">
-        <v>31616240</v>
+        <v>76542872</v>
       </c>
       <c r="G35">
         <v>10113689</v>
@@ -1811,10 +1811,10 @@
         <v>118395038</v>
       </c>
       <c r="I35">
-        <v>1740490</v>
+        <v>5730027</v>
       </c>
       <c r="J35">
-        <v>39377</v>
+        <v>129636</v>
       </c>
       <c r="K35">
         <v>364.7</v>
@@ -1823,7 +1823,7 @@
         <v>0.9859</v>
       </c>
       <c r="M35">
-        <v>462735484</v>
+        <v>876579143</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1831,7 +1831,7 @@
         <v>45166</v>
       </c>
       <c r="B36">
-        <v>116524450</v>
+        <v>223206139</v>
       </c>
       <c r="C36">
         <v>13350661</v>
@@ -1840,10 +1840,10 @@
         <v>53.2</v>
       </c>
       <c r="E36">
-        <v>3831705</v>
+        <v>9650968</v>
       </c>
       <c r="F36">
-        <v>18392898</v>
+        <v>46326441</v>
       </c>
       <c r="G36">
         <v>11149160</v>
@@ -1852,10 +1852,10 @@
         <v>135389237</v>
       </c>
       <c r="I36">
-        <v>2460667</v>
+        <v>7880010</v>
       </c>
       <c r="J36">
-        <v>50327</v>
+        <v>161166</v>
       </c>
       <c r="K36">
         <v>87.3</v>
@@ -1864,7 +1864,7 @@
         <v>1.0241</v>
       </c>
       <c r="M36">
-        <v>496008085</v>
+        <v>939608821</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1872,7 +1872,7 @@
         <v>45173</v>
       </c>
       <c r="B37">
-        <v>108669356</v>
+        <v>207282885</v>
       </c>
       <c r="C37">
         <v>12161326</v>
@@ -1881,10 +1881,10 @@
         <v>47</v>
       </c>
       <c r="E37">
-        <v>2863107</v>
+        <v>7753455</v>
       </c>
       <c r="F37">
-        <v>13880015</v>
+        <v>37587863</v>
       </c>
       <c r="G37">
         <v>6686152</v>
@@ -1893,10 +1893,10 @@
         <v>83095820</v>
       </c>
       <c r="I37">
-        <v>1229500</v>
+        <v>4121405</v>
       </c>
       <c r="J37">
-        <v>26037</v>
+        <v>87280</v>
       </c>
       <c r="K37">
         <v>131.2</v>
@@ -1905,7 +1905,7 @@
         <v>1.001</v>
       </c>
       <c r="M37">
-        <v>472567523</v>
+        <v>895204386</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1913,7 +1913,7 @@
         <v>45180</v>
       </c>
       <c r="B38">
-        <v>112839319</v>
+        <v>217108222</v>
       </c>
       <c r="C38">
         <v>11929064</v>
@@ -1922,10 +1922,10 @@
         <v>48.7</v>
       </c>
       <c r="E38">
-        <v>5243829</v>
+        <v>12184188</v>
       </c>
       <c r="F38">
-        <v>24962520</v>
+        <v>58001137</v>
       </c>
       <c r="G38">
         <v>276576</v>
@@ -1934,10 +1934,10 @@
         <v>3275136</v>
       </c>
       <c r="I38">
-        <v>2076605</v>
+        <v>6772364</v>
       </c>
       <c r="J38">
-        <v>43270</v>
+        <v>141115</v>
       </c>
       <c r="K38">
         <v>227.2</v>
@@ -1946,7 +1946,7 @@
         <v>1.04</v>
       </c>
       <c r="M38">
-        <v>478196260</v>
+        <v>905867137</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1954,7 +1954,7 @@
         <v>45187</v>
       </c>
       <c r="B39">
-        <v>118841643</v>
+        <v>224893743</v>
       </c>
       <c r="C39">
         <v>5396829</v>
@@ -1963,10 +1963,10 @@
         <v>22.2</v>
       </c>
       <c r="E39">
-        <v>3927861</v>
+        <v>9554652</v>
       </c>
       <c r="F39">
-        <v>19120262</v>
+        <v>46510668</v>
       </c>
       <c r="G39">
         <v>5714293</v>
@@ -1975,10 +1975,10 @@
         <v>70549558</v>
       </c>
       <c r="I39">
-        <v>2569499</v>
+        <v>8463845</v>
       </c>
       <c r="J39">
-        <v>57924</v>
+        <v>190801</v>
       </c>
       <c r="K39">
         <v>158.5</v>
@@ -1987,7 +1987,7 @@
         <v>1.0042</v>
       </c>
       <c r="M39">
-        <v>520836472</v>
+        <v>986642272</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1995,7 +1995,7 @@
         <v>45194</v>
       </c>
       <c r="B40">
-        <v>124067768</v>
+        <v>232947154</v>
       </c>
       <c r="C40">
         <v>12456401</v>
@@ -2004,10 +2004,10 @@
         <v>46.2</v>
       </c>
       <c r="E40">
-        <v>8040486</v>
+        <v>18800146</v>
       </c>
       <c r="F40">
-        <v>37867666</v>
+        <v>88541618</v>
       </c>
       <c r="G40">
         <v>9397495</v>
@@ -2016,10 +2016,10 @@
         <v>110076806</v>
       </c>
       <c r="I40">
-        <v>1676382</v>
+        <v>5646385</v>
       </c>
       <c r="J40">
-        <v>34945</v>
+        <v>117702</v>
       </c>
       <c r="K40">
         <v>122.4</v>
@@ -2028,7 +2028,7 @@
         <v>1.0122</v>
       </c>
       <c r="M40">
-        <v>529718380</v>
+        <v>1003467640</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -2036,7 +2036,7 @@
         <v>45201</v>
       </c>
       <c r="B41">
-        <v>123246754</v>
+        <v>230539662</v>
       </c>
       <c r="C41">
         <v>17199562</v>
@@ -2045,10 +2045,10 @@
         <v>64.8</v>
       </c>
       <c r="E41">
-        <v>5631509</v>
+        <v>13045634</v>
       </c>
       <c r="F41">
-        <v>27482278</v>
+        <v>63663887</v>
       </c>
       <c r="G41">
         <v>8643223</v>
@@ -2057,10 +2057,10 @@
         <v>104051375</v>
       </c>
       <c r="I41">
-        <v>1783401</v>
+        <v>5739677</v>
       </c>
       <c r="J41">
-        <v>37631</v>
+        <v>121111</v>
       </c>
       <c r="K41">
         <v>217.2</v>
@@ -2069,7 +2069,7 @@
         <v>1.0231</v>
       </c>
       <c r="M41">
-        <v>530667874</v>
+        <v>1005266307</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2077,7 +2077,7 @@
         <v>45208</v>
       </c>
       <c r="B42">
-        <v>124293055</v>
+        <v>233428402</v>
       </c>
       <c r="C42">
         <v>8970573</v>
@@ -2086,10 +2086,10 @@
         <v>35.3</v>
       </c>
       <c r="E42">
-        <v>3405565</v>
+        <v>8321365</v>
       </c>
       <c r="F42">
-        <v>16918962</v>
+        <v>41340824</v>
       </c>
       <c r="G42">
         <v>10398400</v>
@@ -2098,10 +2098,10 @@
         <v>120236149</v>
       </c>
       <c r="I42">
-        <v>2206083</v>
+        <v>7225078</v>
       </c>
       <c r="J42">
-        <v>49984</v>
+        <v>163702</v>
       </c>
       <c r="K42">
         <v>20.6</v>
@@ -2110,7 +2110,7 @@
         <v>1.0233</v>
       </c>
       <c r="M42">
-        <v>522207122</v>
+        <v>989238750</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2118,7 +2118,7 @@
         <v>45215</v>
       </c>
       <c r="B43">
-        <v>120393126</v>
+        <v>227221219</v>
       </c>
       <c r="C43">
         <v>5497377</v>
@@ -2127,10 +2127,10 @@
         <v>21.1</v>
       </c>
       <c r="E43">
-        <v>4966540</v>
+        <v>12328229</v>
       </c>
       <c r="F43">
-        <v>23299366</v>
+        <v>57835017</v>
       </c>
       <c r="G43">
         <v>6842648</v>
@@ -2139,10 +2139,10 @@
         <v>80146837</v>
       </c>
       <c r="I43">
-        <v>1387437</v>
+        <v>4512337</v>
       </c>
       <c r="J43">
-        <v>30944</v>
+        <v>100638</v>
       </c>
       <c r="K43">
         <v>118.7</v>
@@ -2151,7 +2151,7 @@
         <v>1.0211</v>
       </c>
       <c r="M43">
-        <v>519565576</v>
+        <v>984234759</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2159,7 +2159,7 @@
         <v>45222</v>
       </c>
       <c r="B44">
-        <v>118430671</v>
+        <v>225897068</v>
       </c>
       <c r="C44">
         <v>11568601</v>
@@ -2168,10 +2168,10 @@
         <v>45.8</v>
       </c>
       <c r="E44">
-        <v>3846105</v>
+        <v>9069272</v>
       </c>
       <c r="F44">
-        <v>18476127</v>
+        <v>43567456</v>
       </c>
       <c r="G44">
         <v>4455375</v>
@@ -2180,10 +2180,10 @@
         <v>52621166</v>
       </c>
       <c r="I44">
-        <v>1605532</v>
+        <v>5470156</v>
       </c>
       <c r="J44">
-        <v>34493</v>
+        <v>117519</v>
       </c>
       <c r="K44">
         <v>163.1</v>
@@ -2192,7 +2192,7 @@
         <v>1.018</v>
       </c>
       <c r="M44">
-        <v>514558342</v>
+        <v>974749346</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2200,7 +2200,7 @@
         <v>45229</v>
       </c>
       <c r="B45">
-        <v>117158151</v>
+        <v>218346944</v>
       </c>
       <c r="C45">
         <v>170404</v>
@@ -2209,10 +2209,10 @@
         <v>0.7</v>
       </c>
       <c r="E45">
-        <v>5417984</v>
+        <v>12593403</v>
       </c>
       <c r="F45">
-        <v>25238742</v>
+        <v>58664197</v>
       </c>
       <c r="G45">
         <v>6187792</v>
@@ -2221,10 +2221,10 @@
         <v>73977588</v>
       </c>
       <c r="I45">
-        <v>912338</v>
+        <v>3057288</v>
       </c>
       <c r="J45">
-        <v>19096</v>
+        <v>63993</v>
       </c>
       <c r="K45">
         <v>100.5</v>
@@ -2233,7 +2233,7 @@
         <v>1.0295</v>
       </c>
       <c r="M45">
-        <v>527052389</v>
+        <v>998417342</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2241,7 +2241,7 @@
         <v>45236</v>
       </c>
       <c r="B46">
-        <v>117673739</v>
+        <v>226423436</v>
       </c>
       <c r="C46">
         <v>15780187</v>
@@ -2250,10 +2250,10 @@
         <v>60.5</v>
       </c>
       <c r="E46">
-        <v>2725857</v>
+        <v>6945834</v>
       </c>
       <c r="F46">
-        <v>12974856</v>
+        <v>33061602</v>
       </c>
       <c r="G46">
         <v>93349</v>
@@ -2262,10 +2262,10 @@
         <v>1117480</v>
       </c>
       <c r="I46">
-        <v>1971726</v>
+        <v>6441688</v>
       </c>
       <c r="J46">
-        <v>42695</v>
+        <v>139487</v>
       </c>
       <c r="K46">
         <v>115.2</v>
@@ -2274,7 +2274,7 @@
         <v>0.9911</v>
       </c>
       <c r="M46">
-        <v>563353713</v>
+        <v>1067184455</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2282,7 +2282,7 @@
         <v>45243</v>
       </c>
       <c r="B47">
-        <v>120393248</v>
+        <v>234204112</v>
       </c>
       <c r="C47">
         <v>15035248</v>
@@ -2291,10 +2291,10 @@
         <v>59.4</v>
       </c>
       <c r="E47">
-        <v>3504322</v>
+        <v>9432312</v>
       </c>
       <c r="F47">
-        <v>16272014</v>
+        <v>43798120</v>
       </c>
       <c r="G47">
         <v>3645651</v>
@@ -2303,10 +2303,10 @@
         <v>43104428</v>
       </c>
       <c r="I47">
-        <v>1993024</v>
+        <v>6496029</v>
       </c>
       <c r="J47">
-        <v>42461</v>
+        <v>138396</v>
       </c>
       <c r="K47">
         <v>34.1</v>
@@ -2315,7 +2315,7 @@
         <v>1.0031</v>
       </c>
       <c r="M47">
-        <v>541587705</v>
+        <v>1025952198</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2323,7 +2323,7 @@
         <v>45250</v>
       </c>
       <c r="B48">
-        <v>117872752</v>
+        <v>226228003</v>
       </c>
       <c r="C48">
         <v>6641014</v>
@@ -2332,10 +2332,10 @@
         <v>25.2</v>
       </c>
       <c r="E48">
-        <v>4123932</v>
+        <v>9614257</v>
       </c>
       <c r="F48">
-        <v>19794020</v>
+        <v>46146446</v>
       </c>
       <c r="G48">
         <v>4382629</v>
@@ -2344,10 +2344,10 @@
         <v>51650303</v>
       </c>
       <c r="I48">
-        <v>1114381</v>
+        <v>3613090</v>
       </c>
       <c r="J48">
-        <v>24582</v>
+        <v>79702</v>
       </c>
       <c r="K48">
         <v>68.8</v>
@@ -2356,7 +2356,7 @@
         <v>1.0245</v>
       </c>
       <c r="M48">
-        <v>534033462</v>
+        <v>1011641880</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2364,7 +2364,7 @@
         <v>45257</v>
       </c>
       <c r="B49">
-        <v>115392472</v>
+        <v>219440365</v>
       </c>
       <c r="C49">
         <v>443416</v>
@@ -2373,10 +2373,10 @@
         <v>1.6</v>
       </c>
       <c r="E49">
-        <v>1542218</v>
+        <v>4186764</v>
       </c>
       <c r="F49">
-        <v>7241754</v>
+        <v>19659683</v>
       </c>
       <c r="G49">
         <v>7556783</v>
@@ -2385,10 +2385,10 @@
         <v>94757670</v>
       </c>
       <c r="I49">
-        <v>1803754</v>
+        <v>5841722</v>
       </c>
       <c r="J49">
-        <v>37493</v>
+        <v>121428</v>
       </c>
       <c r="K49">
         <v>50.2</v>
@@ -2397,7 +2397,7 @@
         <v>1.0182</v>
       </c>
       <c r="M49">
-        <v>584193647</v>
+        <v>1106662413</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2405,7 +2405,7 @@
         <v>45264</v>
       </c>
       <c r="B50">
-        <v>120770841</v>
+        <v>234089665</v>
       </c>
       <c r="C50">
         <v>15183319</v>
@@ -2414,10 +2414,10 @@
         <v>57.2</v>
       </c>
       <c r="E50">
-        <v>2833803</v>
+        <v>7233818</v>
       </c>
       <c r="F50">
-        <v>13929748</v>
+        <v>35558320</v>
       </c>
       <c r="G50">
         <v>10678960</v>
@@ -2426,10 +2426,10 @@
         <v>125550413</v>
       </c>
       <c r="I50">
-        <v>2306521</v>
+        <v>7481005</v>
       </c>
       <c r="J50">
-        <v>50812</v>
+        <v>164805</v>
       </c>
       <c r="K50">
         <v>129.6</v>
@@ -2438,7 +2438,7 @@
         <v>0.9874000000000001</v>
       </c>
       <c r="M50">
-        <v>563176656</v>
+        <v>1066849049</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2446,7 +2446,7 @@
         <v>45271</v>
       </c>
       <c r="B51">
-        <v>130455290</v>
+        <v>251018451</v>
       </c>
       <c r="C51">
         <v>10256003</v>
@@ -2455,10 +2455,10 @@
         <v>38</v>
       </c>
       <c r="E51">
-        <v>8328433</v>
+        <v>19267802</v>
       </c>
       <c r="F51">
-        <v>38647564</v>
+        <v>89411007</v>
       </c>
       <c r="G51">
         <v>5582780</v>
@@ -2467,10 +2467,10 @@
         <v>65224293</v>
       </c>
       <c r="I51">
-        <v>1605400</v>
+        <v>5126350</v>
       </c>
       <c r="J51">
-        <v>33212</v>
+        <v>106052</v>
       </c>
       <c r="K51">
         <v>171</v>
@@ -2479,7 +2479,7 @@
         <v>1.0112</v>
       </c>
       <c r="M51">
-        <v>604707186</v>
+        <v>1145522065</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2487,7 +2487,7 @@
         <v>45278</v>
       </c>
       <c r="B52">
-        <v>131204922</v>
+        <v>251850686</v>
       </c>
       <c r="C52">
         <v>14704754</v>
@@ -2496,10 +2496,10 @@
         <v>55.3</v>
       </c>
       <c r="E52">
-        <v>3687564</v>
+        <v>9251857</v>
       </c>
       <c r="F52">
-        <v>19075578</v>
+        <v>47859381</v>
       </c>
       <c r="G52">
         <v>5763083</v>
@@ -2508,10 +2508,10 @@
         <v>65863380</v>
       </c>
       <c r="I52">
-        <v>2139027</v>
+        <v>6808676</v>
       </c>
       <c r="J52">
-        <v>47386</v>
+        <v>150835</v>
       </c>
       <c r="K52">
         <v>129.7</v>
@@ -2520,7 +2520,7 @@
         <v>0.9483</v>
       </c>
       <c r="M52">
-        <v>594856994</v>
+        <v>1126862435</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2528,7 +2528,7 @@
         <v>45285</v>
       </c>
       <c r="B53">
-        <v>133716153</v>
+        <v>253984563</v>
       </c>
       <c r="C53">
         <v>10383037</v>
@@ -2537,10 +2537,10 @@
         <v>38.6</v>
       </c>
       <c r="E53">
-        <v>4868322</v>
+        <v>12076553</v>
       </c>
       <c r="F53">
-        <v>24668252</v>
+        <v>61193048</v>
       </c>
       <c r="G53">
         <v>4661662</v>
@@ -2549,10 +2549,10 @@
         <v>57709487</v>
       </c>
       <c r="I53">
-        <v>2361193</v>
+        <v>7518050</v>
       </c>
       <c r="J53">
-        <v>51879</v>
+        <v>165184</v>
       </c>
       <c r="K53">
         <v>157.4</v>
@@ -2561,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="M53">
-        <v>580110429</v>
+        <v>1098927402</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2569,7 +2569,7 @@
         <v>45292</v>
       </c>
       <c r="B54">
-        <v>128459128</v>
+        <v>233991414</v>
       </c>
       <c r="C54">
         <v>339968</v>
@@ -2578,10 +2578,10 @@
         <v>1.3</v>
       </c>
       <c r="E54">
-        <v>6651396</v>
+        <v>15570788</v>
       </c>
       <c r="F54">
-        <v>30984684</v>
+        <v>72534543</v>
       </c>
       <c r="G54">
         <v>4776453</v>
@@ -2590,10 +2590,10 @@
         <v>57458818</v>
       </c>
       <c r="I54">
-        <v>477153</v>
+        <v>1621654</v>
       </c>
       <c r="J54">
-        <v>10238</v>
+        <v>34794</v>
       </c>
       <c r="K54">
         <v>33.9</v>
@@ -2602,7 +2602,7 @@
         <v>0.9933999999999999</v>
       </c>
       <c r="M54">
-        <v>620456047</v>
+        <v>1175355790</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2610,7 +2610,7 @@
         <v>45299</v>
       </c>
       <c r="B55">
-        <v>133951394</v>
+        <v>252047998</v>
       </c>
       <c r="C55">
         <v>6064741</v>
@@ -2619,10 +2619,10 @@
         <v>22.8</v>
       </c>
       <c r="E55">
-        <v>5757238</v>
+        <v>13378787</v>
       </c>
       <c r="F55">
-        <v>26497315</v>
+        <v>61575000</v>
       </c>
       <c r="G55">
         <v>196036</v>
@@ -2631,10 +2631,10 @@
         <v>2232460</v>
       </c>
       <c r="I55">
-        <v>2611240</v>
+        <v>8477473</v>
       </c>
       <c r="J55">
-        <v>55994</v>
+        <v>181787</v>
       </c>
       <c r="K55">
         <v>34.2</v>
@@ -2643,7 +2643,7 @@
         <v>0.9873</v>
       </c>
       <c r="M55">
-        <v>545100483</v>
+        <v>1032606599</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2651,7 +2651,7 @@
         <v>45306</v>
       </c>
       <c r="B56">
-        <v>128714724</v>
+        <v>241687490</v>
       </c>
       <c r="C56">
         <v>3261747</v>
@@ -2660,10 +2660,10 @@
         <v>12.7</v>
       </c>
       <c r="E56">
-        <v>4695136</v>
+        <v>11196898</v>
       </c>
       <c r="F56">
-        <v>22642996</v>
+        <v>53998718</v>
       </c>
       <c r="G56">
         <v>6477590</v>
@@ -2672,10 +2672,10 @@
         <v>81513158</v>
       </c>
       <c r="I56">
-        <v>1467997</v>
+        <v>4839088</v>
       </c>
       <c r="J56">
-        <v>30363</v>
+        <v>100088</v>
       </c>
       <c r="K56">
         <v>63.2</v>
@@ -2684,7 +2684,7 @@
         <v>1.0188</v>
       </c>
       <c r="M56">
-        <v>610807710</v>
+        <v>1157078542</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2692,7 +2692,7 @@
         <v>45313</v>
       </c>
       <c r="B57">
-        <v>120975560</v>
+        <v>226125359</v>
       </c>
       <c r="C57">
         <v>5115766</v>
@@ -2701,10 +2701,10 @@
         <v>20.1</v>
       </c>
       <c r="E57">
-        <v>3710892</v>
+        <v>9830942</v>
       </c>
       <c r="F57">
-        <v>17963334</v>
+        <v>47588692</v>
       </c>
       <c r="G57">
         <v>10588669</v>
@@ -2713,10 +2713,10 @@
         <v>127481004</v>
       </c>
       <c r="I57">
-        <v>853453</v>
+        <v>2857688</v>
       </c>
       <c r="J57">
-        <v>17231</v>
+        <v>57696</v>
       </c>
       <c r="K57">
         <v>100.3</v>
@@ -2725,7 +2725,7 @@
         <v>0.9791</v>
       </c>
       <c r="M57">
-        <v>562213875</v>
+        <v>1065025212</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2733,7 +2733,7 @@
         <v>45320</v>
       </c>
       <c r="B58">
-        <v>119577025</v>
+        <v>229962399</v>
       </c>
       <c r="C58">
         <v>14494812</v>
@@ -2742,10 +2742,10 @@
         <v>56</v>
       </c>
       <c r="E58">
-        <v>1811908</v>
+        <v>4280659</v>
       </c>
       <c r="F58">
-        <v>8650769</v>
+        <v>20437570</v>
       </c>
       <c r="G58">
         <v>7805400</v>
@@ -2754,10 +2754,10 @@
         <v>98685416</v>
       </c>
       <c r="I58">
-        <v>2239823</v>
+        <v>7373064</v>
       </c>
       <c r="J58">
-        <v>46290</v>
+        <v>152376</v>
       </c>
       <c r="K58">
         <v>135.1</v>
@@ -2766,7 +2766,7 @@
         <v>1.0428</v>
       </c>
       <c r="M58">
-        <v>589133163</v>
+        <v>1116019543</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2774,7 +2774,7 @@
         <v>45327</v>
       </c>
       <c r="B59">
-        <v>114357441</v>
+        <v>215749279</v>
       </c>
       <c r="C59">
         <v>14621566</v>
@@ -2783,10 +2783,10 @@
         <v>55.6</v>
       </c>
       <c r="E59">
-        <v>1508494</v>
+        <v>4060483</v>
       </c>
       <c r="F59">
-        <v>7242710</v>
+        <v>19495541</v>
       </c>
       <c r="G59">
         <v>10669989</v>
@@ -2795,10 +2795,10 @@
         <v>131953494</v>
       </c>
       <c r="I59">
-        <v>1099091</v>
+        <v>3679346</v>
       </c>
       <c r="J59">
-        <v>23678</v>
+        <v>79265</v>
       </c>
       <c r="K59">
         <v>58.3</v>
@@ -2807,7 +2807,7 @@
         <v>1.002</v>
       </c>
       <c r="M59">
-        <v>597600239</v>
+        <v>1132059080</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2815,7 +2815,7 @@
         <v>45334</v>
       </c>
       <c r="B60">
-        <v>108658097</v>
+        <v>197141494</v>
       </c>
       <c r="C60">
         <v>9672999</v>
@@ -2824,10 +2824,10 @@
         <v>36</v>
       </c>
       <c r="E60">
-        <v>88845</v>
+        <v>216238</v>
       </c>
       <c r="F60">
-        <v>431140</v>
+        <v>1049342</v>
       </c>
       <c r="G60">
         <v>9178432</v>
@@ -2836,10 +2836,10 @@
         <v>113437659</v>
       </c>
       <c r="I60">
-        <v>1216410</v>
+        <v>3983988</v>
       </c>
       <c r="J60">
-        <v>24233</v>
+        <v>79367</v>
       </c>
       <c r="K60">
         <v>35.7</v>
@@ -2848,7 +2848,7 @@
         <v>1.027</v>
       </c>
       <c r="M60">
-        <v>607127810</v>
+        <v>1150107554</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2856,7 +2856,7 @@
         <v>45341</v>
       </c>
       <c r="B61">
-        <v>112428528</v>
+        <v>221835048</v>
       </c>
       <c r="C61">
         <v>15132077</v>
@@ -2865,10 +2865,10 @@
         <v>56.4</v>
       </c>
       <c r="E61">
-        <v>4372344</v>
+        <v>10756279</v>
       </c>
       <c r="F61">
-        <v>20926450</v>
+        <v>51480559</v>
       </c>
       <c r="G61">
         <v>107004</v>
@@ -2877,10 +2877,10 @@
         <v>1267212</v>
       </c>
       <c r="I61">
-        <v>1249910</v>
+        <v>4031736</v>
       </c>
       <c r="J61">
-        <v>26816</v>
+        <v>86497</v>
       </c>
       <c r="K61">
         <v>127</v>
@@ -2889,7 +2889,7 @@
         <v>0.9902</v>
       </c>
       <c r="M61">
-        <v>636206023</v>
+        <v>1205191627</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2897,7 +2897,7 @@
         <v>45348</v>
       </c>
       <c r="B62">
-        <v>119930187</v>
+        <v>238477757</v>
       </c>
       <c r="C62">
         <v>16962223</v>
@@ -2906,10 +2906,10 @@
         <v>58.6</v>
       </c>
       <c r="E62">
-        <v>6235960</v>
+        <v>14426380</v>
       </c>
       <c r="F62">
-        <v>29912773</v>
+        <v>69200737</v>
       </c>
       <c r="G62">
         <v>10867506</v>
@@ -2918,10 +2918,10 @@
         <v>127979238</v>
       </c>
       <c r="I62">
-        <v>1604866</v>
+        <v>5308648</v>
       </c>
       <c r="J62">
-        <v>34088</v>
+        <v>112757</v>
       </c>
       <c r="K62">
         <v>197.3</v>
@@ -2930,7 +2930,7 @@
         <v>1.0737</v>
       </c>
       <c r="M62">
-        <v>587731969</v>
+        <v>1113365204</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2938,7 +2938,7 @@
         <v>45355</v>
       </c>
       <c r="B63">
-        <v>119925473</v>
+        <v>236428536</v>
       </c>
       <c r="C63">
         <v>14363349</v>
@@ -2947,10 +2947,10 @@
         <v>56.2</v>
       </c>
       <c r="E63">
-        <v>3764415</v>
+        <v>9948293</v>
       </c>
       <c r="F63">
-        <v>18263969</v>
+        <v>48266551</v>
       </c>
       <c r="G63">
         <v>7378284</v>
@@ -2959,10 +2959,10 @@
         <v>88023785</v>
       </c>
       <c r="I63">
-        <v>1458903</v>
+        <v>5032016</v>
       </c>
       <c r="J63">
-        <v>28884</v>
+        <v>99628</v>
       </c>
       <c r="K63">
         <v>25.1</v>
@@ -2971,7 +2971,7 @@
         <v>0.9764</v>
       </c>
       <c r="M63">
-        <v>606008084</v>
+        <v>1147986410</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2979,7 +2979,7 @@
         <v>45362</v>
       </c>
       <c r="B64">
-        <v>122330488</v>
+        <v>233540535</v>
       </c>
       <c r="C64">
         <v>406340</v>
@@ -2988,10 +2988,10 @@
         <v>1.5</v>
       </c>
       <c r="E64">
-        <v>2388910</v>
+        <v>6076370</v>
       </c>
       <c r="F64">
-        <v>10559809</v>
+        <v>26859661</v>
       </c>
       <c r="G64">
         <v>8552893</v>
@@ -3000,10 +3000,10 @@
         <v>100526286</v>
       </c>
       <c r="I64">
-        <v>2992819</v>
+        <v>9733474</v>
       </c>
       <c r="J64">
-        <v>63450</v>
+        <v>206356</v>
       </c>
       <c r="K64">
         <v>24</v>
@@ -3012,7 +3012,7 @@
         <v>1.0438</v>
       </c>
       <c r="M64">
-        <v>569416454</v>
+        <v>1078669359</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -3020,7 +3020,7 @@
         <v>45369</v>
       </c>
       <c r="B65">
-        <v>112604841</v>
+        <v>216776965</v>
       </c>
       <c r="C65">
         <v>5026146</v>
@@ -3029,10 +3029,10 @@
         <v>17.9</v>
       </c>
       <c r="E65">
-        <v>3761364</v>
+        <v>9832156</v>
       </c>
       <c r="F65">
-        <v>17711821</v>
+        <v>46298459</v>
       </c>
       <c r="G65">
         <v>5244720</v>
@@ -3041,10 +3041,10 @@
         <v>61926206</v>
       </c>
       <c r="I65">
-        <v>1058409</v>
+        <v>3653099</v>
       </c>
       <c r="J65">
-        <v>22000</v>
+        <v>75934</v>
       </c>
       <c r="K65">
         <v>233.6</v>
@@ -3053,7 +3053,7 @@
         <v>1.0253</v>
       </c>
       <c r="M65">
-        <v>522253832</v>
+        <v>989327234</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -3061,7 +3061,7 @@
         <v>45376</v>
       </c>
       <c r="B66">
-        <v>114077876</v>
+        <v>221135381</v>
       </c>
       <c r="C66">
         <v>7668206</v>
@@ -3070,10 +3070,10 @@
         <v>28.9</v>
       </c>
       <c r="E66">
-        <v>4148653</v>
+        <v>10149775</v>
       </c>
       <c r="F66">
-        <v>18962146</v>
+        <v>46391328</v>
       </c>
       <c r="G66">
         <v>186999</v>
@@ -3082,10 +3082,10 @@
         <v>2156004</v>
       </c>
       <c r="I66">
-        <v>1851000</v>
+        <v>5891916</v>
       </c>
       <c r="J66">
-        <v>37791</v>
+        <v>120294</v>
       </c>
       <c r="K66">
         <v>107.8</v>
@@ -3094,7 +3094,7 @@
         <v>0.9866</v>
       </c>
       <c r="M66">
-        <v>522460912</v>
+        <v>989719515</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -3102,7 +3102,7 @@
         <v>45383</v>
       </c>
       <c r="B67">
-        <v>112976906</v>
+        <v>221426258</v>
       </c>
       <c r="C67">
         <v>18026574</v>
@@ -3111,10 +3111,10 @@
         <v>72.59999999999999</v>
       </c>
       <c r="E67">
-        <v>3054779</v>
+        <v>8074434</v>
       </c>
       <c r="F67">
-        <v>15123598</v>
+        <v>39974905</v>
       </c>
       <c r="G67">
         <v>6770188</v>
@@ -3123,10 +3123,10 @@
         <v>81293977</v>
       </c>
       <c r="I67">
-        <v>1573971</v>
+        <v>5118645</v>
       </c>
       <c r="J67">
-        <v>34651</v>
+        <v>112688</v>
       </c>
       <c r="K67">
         <v>52.5</v>
@@ -3135,7 +3135,7 @@
         <v>1.0166</v>
       </c>
       <c r="M67">
-        <v>562413835</v>
+        <v>1065404005</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -3143,7 +3143,7 @@
         <v>45390</v>
       </c>
       <c r="B68">
-        <v>109619501</v>
+        <v>214277774</v>
       </c>
       <c r="C68">
         <v>8303121</v>
@@ -3152,10 +3152,10 @@
         <v>31.9</v>
       </c>
       <c r="E68">
-        <v>4083325</v>
+        <v>10549097</v>
       </c>
       <c r="F68">
-        <v>18220180</v>
+        <v>47071066</v>
       </c>
       <c r="G68">
         <v>12079567</v>
@@ -3164,10 +3164,10 @@
         <v>140214772</v>
       </c>
       <c r="I68">
-        <v>1139410</v>
+        <v>3859564</v>
       </c>
       <c r="J68">
-        <v>23450</v>
+        <v>79432</v>
       </c>
       <c r="K68">
         <v>43.1</v>
@@ -3176,7 +3176,7 @@
         <v>1.0489</v>
       </c>
       <c r="M68">
-        <v>490737989</v>
+        <v>929625457</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -3184,7 +3184,7 @@
         <v>45397</v>
       </c>
       <c r="B69">
-        <v>109248084</v>
+        <v>210575209</v>
       </c>
       <c r="C69">
         <v>368022</v>
@@ -3193,10 +3193,10 @@
         <v>1.4</v>
       </c>
       <c r="E69">
-        <v>4695217</v>
+        <v>11140954</v>
       </c>
       <c r="F69">
-        <v>21610247</v>
+        <v>51277449</v>
       </c>
       <c r="G69">
         <v>8698809</v>
@@ -3205,10 +3205,10 @@
         <v>103602934</v>
       </c>
       <c r="I69">
-        <v>1171189</v>
+        <v>3895593</v>
       </c>
       <c r="J69">
-        <v>22906</v>
+        <v>76189</v>
       </c>
       <c r="K69">
         <v>44.6</v>
@@ -3217,7 +3217,7 @@
         <v>1.0039</v>
       </c>
       <c r="M69">
-        <v>549685855</v>
+        <v>1041292861</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -3225,7 +3225,7 @@
         <v>45404</v>
       </c>
       <c r="B70">
-        <v>119291477</v>
+        <v>225414930</v>
       </c>
       <c r="C70">
         <v>255181</v>
@@ -3234,10 +3234,10 @@
         <v>0.9</v>
       </c>
       <c r="E70">
-        <v>8357963</v>
+        <v>19257302</v>
       </c>
       <c r="F70">
-        <v>40326827</v>
+        <v>92915691</v>
       </c>
       <c r="G70">
         <v>7215529</v>
@@ -3246,10 +3246,10 @@
         <v>85454814</v>
       </c>
       <c r="I70">
-        <v>1831278</v>
+        <v>5836159</v>
       </c>
       <c r="J70">
-        <v>40244</v>
+        <v>128256</v>
       </c>
       <c r="K70">
         <v>96.2</v>
@@ -3258,7 +3258,7 @@
         <v>0.9916</v>
       </c>
       <c r="M70">
-        <v>490698825</v>
+        <v>929551268</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -3266,7 +3266,7 @@
         <v>45411</v>
       </c>
       <c r="B71">
-        <v>116407208</v>
+        <v>216760836</v>
       </c>
       <c r="C71">
         <v>6128817</v>
@@ -3275,10 +3275,10 @@
         <v>23.1</v>
       </c>
       <c r="E71">
-        <v>6088690</v>
+        <v>14006399</v>
       </c>
       <c r="F71">
-        <v>29003381</v>
+        <v>66719270</v>
       </c>
       <c r="G71">
         <v>6101866</v>
@@ -3287,10 +3287,10 @@
         <v>73003671</v>
       </c>
       <c r="I71">
-        <v>1314636</v>
+        <v>4319978</v>
       </c>
       <c r="J71">
-        <v>26904</v>
+        <v>88407</v>
       </c>
       <c r="K71">
         <v>97</v>
@@ -3299,7 +3299,7 @@
         <v>1.0122</v>
       </c>
       <c r="M71">
-        <v>539406593</v>
+        <v>1021820427</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -3307,7 +3307,7 @@
         <v>45418</v>
       </c>
       <c r="B72">
-        <v>112576979</v>
+        <v>214816133</v>
       </c>
       <c r="C72">
         <v>16617408</v>
@@ -3316,10 +3316,10 @@
         <v>64.5</v>
       </c>
       <c r="E72">
-        <v>3938879</v>
+        <v>9143192</v>
       </c>
       <c r="F72">
-        <v>19628340</v>
+        <v>45562631</v>
       </c>
       <c r="G72">
         <v>10191021</v>
@@ -3328,10 +3328,10 @@
         <v>113873586</v>
       </c>
       <c r="I72">
-        <v>1583482</v>
+        <v>5228121</v>
       </c>
       <c r="J72">
-        <v>33005</v>
+        <v>108970</v>
       </c>
       <c r="K72">
         <v>183.6</v>
@@ -3340,7 +3340,7 @@
         <v>1.0022</v>
       </c>
       <c r="M72">
-        <v>526883050</v>
+        <v>998096556</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -3348,7 +3348,7 @@
         <v>45425</v>
       </c>
       <c r="B73">
-        <v>110308909</v>
+        <v>208505977</v>
       </c>
       <c r="C73">
         <v>6988824</v>
@@ -3357,10 +3357,10 @@
         <v>26.7</v>
       </c>
       <c r="E73">
-        <v>5179656</v>
+        <v>12260934</v>
       </c>
       <c r="F73">
-        <v>25633184</v>
+        <v>60677156</v>
       </c>
       <c r="G73">
         <v>257550</v>
@@ -3369,10 +3369,10 @@
         <v>3138657</v>
       </c>
       <c r="I73">
-        <v>1065782</v>
+        <v>3675750</v>
       </c>
       <c r="J73">
-        <v>22449</v>
+        <v>77423</v>
       </c>
       <c r="K73">
         <v>15.3</v>
@@ -3381,7 +3381,7 @@
         <v>1.0288</v>
       </c>
       <c r="M73">
-        <v>489325679</v>
+        <v>926950061</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -3389,7 +3389,7 @@
         <v>45432</v>
       </c>
       <c r="B74">
-        <v>104619169</v>
+        <v>201570890</v>
       </c>
       <c r="C74">
         <v>6514866</v>
@@ -3398,10 +3398,10 @@
         <v>23.9</v>
       </c>
       <c r="E74">
-        <v>3492037</v>
+        <v>8741884</v>
       </c>
       <c r="F74">
-        <v>15643912</v>
+        <v>39162613</v>
       </c>
       <c r="G74">
         <v>318327</v>
@@ -3410,10 +3410,10 @@
         <v>3740770</v>
       </c>
       <c r="I74">
-        <v>1648955</v>
+        <v>5707224</v>
       </c>
       <c r="J74">
-        <v>33665</v>
+        <v>116520</v>
       </c>
       <c r="K74">
         <v>140.3</v>
@@ -3422,7 +3422,7 @@
         <v>1.0412</v>
       </c>
       <c r="M74">
-        <v>500088310</v>
+        <v>947338161</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -3430,7 +3430,7 @@
         <v>45439</v>
       </c>
       <c r="B75">
-        <v>122470982</v>
+        <v>217818394</v>
       </c>
       <c r="C75">
         <v>11985097</v>
@@ -3439,10 +3439,10 @@
         <v>43.4</v>
       </c>
       <c r="E75">
-        <v>16293517</v>
+        <v>37480096</v>
       </c>
       <c r="F75">
-        <v>70865621</v>
+        <v>163012710</v>
       </c>
       <c r="G75">
         <v>10818048</v>
@@ -3451,10 +3451,10 @@
         <v>120365003</v>
       </c>
       <c r="I75">
-        <v>1072606</v>
+        <v>3517392</v>
       </c>
       <c r="J75">
-        <v>22478</v>
+        <v>73711</v>
       </c>
       <c r="K75">
         <v>177.5</v>
@@ -3463,7 +3463,7 @@
         <v>1.0422</v>
       </c>
       <c r="M75">
-        <v>479545648</v>
+        <v>908423339</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -3471,7 +3471,7 @@
         <v>45446</v>
       </c>
       <c r="B76">
-        <v>121326726</v>
+        <v>224252955</v>
       </c>
       <c r="C76">
         <v>11071965</v>
@@ -3480,10 +3480,10 @@
         <v>41</v>
       </c>
       <c r="E76">
-        <v>6103418</v>
+        <v>14948836</v>
       </c>
       <c r="F76">
-        <v>28171717</v>
+        <v>68999761</v>
       </c>
       <c r="G76">
         <v>6979305</v>
@@ -3492,10 +3492,10 @@
         <v>79766477</v>
       </c>
       <c r="I76">
-        <v>2161448</v>
+        <v>7082851</v>
       </c>
       <c r="J76">
-        <v>44177</v>
+        <v>144763</v>
       </c>
       <c r="K76">
         <v>175.6</v>
@@ -3504,7 +3504,7 @@
         <v>0.9641999999999999</v>
       </c>
       <c r="M76">
-        <v>449780885</v>
+        <v>852038706</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -3512,7 +3512,7 @@
         <v>45453</v>
       </c>
       <c r="B77">
-        <v>126399784</v>
+        <v>227615481</v>
       </c>
       <c r="C77">
         <v>9622292</v>
@@ -3521,10 +3521,10 @@
         <v>36.3</v>
       </c>
       <c r="E77">
-        <v>8444026</v>
+        <v>19495726</v>
       </c>
       <c r="F77">
-        <v>42493152</v>
+        <v>98108990</v>
       </c>
       <c r="G77">
         <v>6378235</v>
@@ -3533,10 +3533,10 @@
         <v>74141107</v>
       </c>
       <c r="I77">
-        <v>2370401</v>
+        <v>7581077</v>
       </c>
       <c r="J77">
-        <v>49340</v>
+        <v>157799</v>
       </c>
       <c r="K77">
         <v>111.4</v>
@@ -3545,7 +3545,7 @@
         <v>1.0629</v>
       </c>
       <c r="M77">
-        <v>453210051</v>
+        <v>858534718</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -3553,7 +3553,7 @@
         <v>45460</v>
       </c>
       <c r="B78">
-        <v>118551745</v>
+        <v>216818863</v>
       </c>
       <c r="C78">
         <v>21100712</v>
@@ -3562,10 +3562,10 @@
         <v>80.2</v>
       </c>
       <c r="E78">
-        <v>3418364</v>
+        <v>8373427</v>
       </c>
       <c r="F78">
-        <v>15812769</v>
+        <v>38734046</v>
       </c>
       <c r="G78">
         <v>9895069</v>
@@ -3574,10 +3574,10 @@
         <v>120271128</v>
       </c>
       <c r="I78">
-        <v>2227236</v>
+        <v>7135442</v>
       </c>
       <c r="J78">
-        <v>47713</v>
+        <v>152860</v>
       </c>
       <c r="K78">
         <v>143.8</v>
@@ -3586,7 +3586,7 @@
         <v>1.0367</v>
       </c>
       <c r="M78">
-        <v>453535504</v>
+        <v>859151237</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -3594,7 +3594,7 @@
         <v>45467</v>
       </c>
       <c r="B79">
-        <v>119335673</v>
+        <v>210645002</v>
       </c>
       <c r="C79">
         <v>5880447</v>
@@ -3603,10 +3603,10 @@
         <v>21.7</v>
       </c>
       <c r="E79">
-        <v>2386366</v>
+        <v>5920000</v>
       </c>
       <c r="F79">
-        <v>11114879</v>
+        <v>27573345</v>
       </c>
       <c r="G79">
         <v>8798573</v>
@@ -3615,10 +3615,10 @@
         <v>101343633</v>
       </c>
       <c r="I79">
-        <v>3868733</v>
+        <v>12340548</v>
       </c>
       <c r="J79">
-        <v>77683</v>
+        <v>247796</v>
       </c>
       <c r="K79">
         <v>162.5</v>
@@ -3627,7 +3627,7 @@
         <v>1.0245</v>
       </c>
       <c r="M79">
-        <v>487735536</v>
+        <v>923937786</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -3635,7 +3635,7 @@
         <v>45474</v>
       </c>
       <c r="B80">
-        <v>109079584</v>
+        <v>197470236</v>
       </c>
       <c r="C80">
         <v>190750</v>
@@ -3644,10 +3644,10 @@
         <v>0.7</v>
       </c>
       <c r="E80">
-        <v>2822348</v>
+        <v>6976065</v>
       </c>
       <c r="F80">
-        <v>13602619</v>
+        <v>33621922</v>
       </c>
       <c r="G80">
         <v>13623616</v>
@@ -3656,10 +3656,10 @@
         <v>168583876</v>
       </c>
       <c r="I80">
-        <v>1962090</v>
+        <v>6306896</v>
       </c>
       <c r="J80">
-        <v>41655</v>
+        <v>133896</v>
       </c>
       <c r="K80">
         <v>158.5</v>
@@ -3668,7 +3668,7 @@
         <v>1.0245</v>
       </c>
       <c r="M80">
-        <v>467295643</v>
+        <v>885217643</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -3676,7 +3676,7 @@
         <v>45481</v>
       </c>
       <c r="B81">
-        <v>93535718</v>
+        <v>160513172</v>
       </c>
       <c r="C81">
         <v>10617184</v>
@@ -3685,10 +3685,10 @@
         <v>39.5</v>
       </c>
       <c r="E81">
-        <v>89543</v>
+        <v>206699</v>
       </c>
       <c r="F81">
-        <v>433833</v>
+        <v>1001443</v>
       </c>
       <c r="G81">
         <v>3472956</v>
@@ -3697,10 +3697,10 @@
         <v>41113315</v>
       </c>
       <c r="I81">
-        <v>851177</v>
+        <v>2855866</v>
       </c>
       <c r="J81">
-        <v>16778</v>
+        <v>56293</v>
       </c>
       <c r="K81">
         <v>154</v>
@@ -3709,7 +3709,7 @@
         <v>1.0107</v>
       </c>
       <c r="M81">
-        <v>483131938</v>
+        <v>915216999</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -3717,7 +3717,7 @@
         <v>45488</v>
       </c>
       <c r="B82">
-        <v>105457213</v>
+        <v>202643323</v>
       </c>
       <c r="C82">
         <v>11326657</v>
@@ -3726,10 +3726,10 @@
         <v>42</v>
       </c>
       <c r="E82">
-        <v>9529475</v>
+        <v>22165731</v>
       </c>
       <c r="F82">
-        <v>43118279</v>
+        <v>100293891</v>
       </c>
       <c r="G82">
         <v>4197994</v>
@@ -3738,10 +3738,10 @@
         <v>48643852</v>
       </c>
       <c r="I82">
-        <v>1160001</v>
+        <v>4010912</v>
       </c>
       <c r="J82">
-        <v>23319</v>
+        <v>80631</v>
       </c>
       <c r="K82">
         <v>212.1</v>
@@ -3750,7 +3750,7 @@
         <v>1.0304</v>
       </c>
       <c r="M82">
-        <v>508031784</v>
+        <v>962385815</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -3758,7 +3758,7 @@
         <v>45495</v>
       </c>
       <c r="B83">
-        <v>102634993</v>
+        <v>200941103</v>
       </c>
       <c r="C83">
         <v>18900208</v>
@@ -3767,10 +3767,10 @@
         <v>72</v>
       </c>
       <c r="E83">
-        <v>2387698</v>
+        <v>6219623</v>
       </c>
       <c r="F83">
-        <v>11222652</v>
+        <v>29233457</v>
       </c>
       <c r="G83">
         <v>11217685</v>
@@ -3779,10 +3779,10 @@
         <v>128809782</v>
       </c>
       <c r="I83">
-        <v>1779349</v>
+        <v>5810745</v>
       </c>
       <c r="J83">
-        <v>36852</v>
+        <v>120347</v>
       </c>
       <c r="K83">
         <v>176.1</v>
@@ -3791,7 +3791,7 @@
         <v>1.0232</v>
       </c>
       <c r="M83">
-        <v>461156398</v>
+        <v>873587815</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -3799,7 +3799,7 @@
         <v>45502</v>
       </c>
       <c r="B84">
-        <v>99850077</v>
+        <v>188845970</v>
       </c>
       <c r="C84">
         <v>11736935</v>
@@ -3808,10 +3808,10 @@
         <v>45.3</v>
       </c>
       <c r="E84">
-        <v>3609582</v>
+        <v>8640463</v>
       </c>
       <c r="F84">
-        <v>16419461</v>
+        <v>39304202</v>
       </c>
       <c r="G84">
         <v>12864554</v>
@@ -3820,10 +3820,10 @@
         <v>153451372</v>
       </c>
       <c r="I84">
-        <v>754815</v>
+        <v>2592355</v>
       </c>
       <c r="J84">
-        <v>15469</v>
+        <v>53127</v>
       </c>
       <c r="K84">
         <v>58.7</v>
@@ -3832,7 +3832,7 @@
         <v>0.9963</v>
       </c>
       <c r="M84">
-        <v>480146632</v>
+        <v>909561808</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3840,7 +3840,7 @@
         <v>45509</v>
       </c>
       <c r="B85">
-        <v>110643410</v>
+        <v>216031946</v>
       </c>
       <c r="C85">
         <v>10711679</v>
@@ -3849,10 +3849,10 @@
         <v>40.5</v>
       </c>
       <c r="E85">
-        <v>7242370</v>
+        <v>16855894</v>
       </c>
       <c r="F85">
-        <v>34671637</v>
+        <v>80694772</v>
       </c>
       <c r="G85">
         <v>10390356</v>
@@ -3861,10 +3861,10 @@
         <v>123403595</v>
       </c>
       <c r="I85">
-        <v>1835296</v>
+        <v>6053555</v>
       </c>
       <c r="J85">
-        <v>36532</v>
+        <v>120498</v>
       </c>
       <c r="K85">
         <v>118.4</v>
@@ -3873,7 +3873,7 @@
         <v>0.9764</v>
       </c>
       <c r="M85">
-        <v>519718785</v>
+        <v>984524990</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3881,7 +3881,7 @@
         <v>45516</v>
       </c>
       <c r="B86">
-        <v>107755554</v>
+        <v>207460066</v>
       </c>
       <c r="C86">
         <v>18935112</v>
@@ -3890,10 +3890,10 @@
         <v>71.3</v>
       </c>
       <c r="E86">
-        <v>4535148</v>
+        <v>11606379</v>
       </c>
       <c r="F86">
-        <v>21129129</v>
+        <v>54073792</v>
       </c>
       <c r="G86">
         <v>6959810</v>
@@ -3902,10 +3902,10 @@
         <v>77512249</v>
       </c>
       <c r="I86">
-        <v>1154105</v>
+        <v>3996791</v>
       </c>
       <c r="J86">
-        <v>22863</v>
+        <v>79176</v>
       </c>
       <c r="K86">
         <v>96.90000000000001</v>
@@ -3914,7 +3914,7 @@
         <v>1.0314</v>
       </c>
       <c r="M86">
-        <v>504868017</v>
+        <v>956392559</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3922,7 +3922,7 @@
         <v>45523</v>
       </c>
       <c r="B87">
-        <v>130499325</v>
+        <v>237427737</v>
       </c>
       <c r="C87">
         <v>8652540</v>
@@ -3931,10 +3931,10 @@
         <v>34.4</v>
       </c>
       <c r="E87">
-        <v>9678371</v>
+        <v>22710085</v>
       </c>
       <c r="F87">
-        <v>46990333</v>
+        <v>110261779</v>
       </c>
       <c r="G87">
         <v>10609867</v>
@@ -3943,10 +3943,10 @@
         <v>118030569</v>
       </c>
       <c r="I87">
-        <v>3843511</v>
+        <v>12309493</v>
       </c>
       <c r="J87">
-        <v>77333</v>
+        <v>247672</v>
       </c>
       <c r="K87">
         <v>106.7</v>
@@ -3955,7 +3955,7 @@
         <v>1.0478</v>
       </c>
       <c r="M87">
-        <v>468443351</v>
+        <v>887391794</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3963,7 +3963,7 @@
         <v>45530</v>
       </c>
       <c r="B88">
-        <v>124590095</v>
+        <v>226015638</v>
       </c>
       <c r="C88">
         <v>5308575</v>
@@ -3972,10 +3972,10 @@
         <v>19.6</v>
       </c>
       <c r="E88">
-        <v>3709022</v>
+        <v>8989088</v>
       </c>
       <c r="F88">
-        <v>17456394</v>
+        <v>42306859</v>
       </c>
       <c r="G88">
         <v>6107042</v>
@@ -3984,10 +3984,10 @@
         <v>69966430</v>
       </c>
       <c r="I88">
-        <v>2663243</v>
+        <v>8668683</v>
       </c>
       <c r="J88">
-        <v>54827</v>
+        <v>178460</v>
       </c>
       <c r="K88">
         <v>52.9</v>
@@ -3996,7 +3996,7 @@
         <v>1.0714</v>
       </c>
       <c r="M88">
-        <v>477494544</v>
+        <v>904537846</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -4004,7 +4004,7 @@
         <v>45537</v>
       </c>
       <c r="B89">
-        <v>135408321</v>
+        <v>239230241</v>
       </c>
       <c r="C89">
         <v>13404424</v>
@@ -4013,10 +4013,10 @@
         <v>47.4</v>
       </c>
       <c r="E89">
-        <v>7900593</v>
+        <v>18427989</v>
       </c>
       <c r="F89">
-        <v>36489901</v>
+        <v>85112026</v>
       </c>
       <c r="G89">
         <v>6771754</v>
@@ -4025,10 +4025,10 @@
         <v>75351464</v>
       </c>
       <c r="I89">
-        <v>3488144</v>
+        <v>11099736</v>
       </c>
       <c r="J89">
-        <v>70513</v>
+        <v>224383</v>
       </c>
       <c r="K89">
         <v>39.6</v>
@@ -4037,7 +4037,7 @@
         <v>0.9769</v>
       </c>
       <c r="M89">
-        <v>505056126</v>
+        <v>956748903</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -4045,7 +4045,7 @@
         <v>45544</v>
       </c>
       <c r="B90">
-        <v>105676991</v>
+        <v>176843202</v>
       </c>
       <c r="C90">
         <v>12763546</v>
@@ -4054,10 +4054,10 @@
         <v>47.9</v>
       </c>
       <c r="E90">
-        <v>168058</v>
+        <v>389136</v>
       </c>
       <c r="F90">
-        <v>771008</v>
+        <v>1785263</v>
       </c>
       <c r="G90">
         <v>6725899</v>
@@ -4066,10 +4066,10 @@
         <v>79592265</v>
       </c>
       <c r="I90">
-        <v>30679</v>
+        <v>104462</v>
       </c>
       <c r="J90">
-        <v>615</v>
+        <v>2094</v>
       </c>
       <c r="K90">
         <v>105.7</v>
@@ -4078,7 +4078,7 @@
         <v>1.0117</v>
       </c>
       <c r="M90">
-        <v>513243596</v>
+        <v>972258769</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -4086,7 +4086,7 @@
         <v>45551</v>
       </c>
       <c r="B91">
-        <v>100539561</v>
+        <v>172721052</v>
       </c>
       <c r="C91">
         <v>162394</v>
@@ -4095,10 +4095,10 @@
         <v>0.6</v>
       </c>
       <c r="E91">
-        <v>3764662</v>
+        <v>9400836</v>
       </c>
       <c r="F91">
-        <v>17247268</v>
+        <v>43068608</v>
       </c>
       <c r="G91">
         <v>4639947</v>
@@ -4107,10 +4107,10 @@
         <v>53177084</v>
       </c>
       <c r="I91">
-        <v>35184</v>
+        <v>113669</v>
       </c>
       <c r="J91">
-        <v>730</v>
+        <v>2359</v>
       </c>
       <c r="K91">
         <v>101.9</v>
@@ -4119,7 +4119,7 @@
         <v>1.0217</v>
       </c>
       <c r="M91">
-        <v>527821539</v>
+        <v>999874375</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -4127,7 +4127,7 @@
         <v>45558</v>
       </c>
       <c r="B92">
-        <v>102445465</v>
+        <v>180996764</v>
       </c>
       <c r="C92">
         <v>6858758</v>
@@ -4136,10 +4136,10 @@
         <v>24.2</v>
       </c>
       <c r="E92">
-        <v>5052492</v>
+        <v>11897655</v>
       </c>
       <c r="F92">
-        <v>23885476</v>
+        <v>56245745</v>
       </c>
       <c r="G92">
         <v>6053562</v>
@@ -4148,10 +4148,10 @@
         <v>72360452</v>
       </c>
       <c r="I92">
-        <v>44119</v>
+        <v>142059</v>
       </c>
       <c r="J92">
-        <v>868</v>
+        <v>2796</v>
       </c>
       <c r="K92">
         <v>144.5</v>
@@ -4160,7 +4160,7 @@
         <v>1.014</v>
       </c>
       <c r="M92">
-        <v>481863084</v>
+        <v>912813355</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -4168,7 +4168,7 @@
         <v>45565</v>
       </c>
       <c r="B93">
-        <v>109882914</v>
+        <v>218360360</v>
       </c>
       <c r="C93">
         <v>8113340</v>
@@ -4177,10 +4177,10 @@
         <v>28.8</v>
       </c>
       <c r="E93">
-        <v>3844757</v>
+        <v>9302252</v>
       </c>
       <c r="F93">
-        <v>17213537</v>
+        <v>41647537</v>
       </c>
       <c r="G93">
         <v>5915057</v>
@@ -4189,10 +4189,10 @@
         <v>70190109</v>
       </c>
       <c r="I93">
-        <v>2665159</v>
+        <v>8510331</v>
       </c>
       <c r="J93">
-        <v>53266</v>
+        <v>170086</v>
       </c>
       <c r="K93">
         <v>183.2</v>
@@ -4201,7 +4201,7 @@
         <v>0.9738</v>
       </c>
       <c r="M93">
-        <v>529966507</v>
+        <v>1003937677</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -4209,7 +4209,7 @@
         <v>45572</v>
       </c>
       <c r="B94">
-        <v>107880366</v>
+        <v>208906318</v>
       </c>
       <c r="C94">
         <v>19388283</v>
@@ -4218,10 +4218,10 @@
         <v>72.7</v>
       </c>
       <c r="E94">
-        <v>3198356</v>
+        <v>8318760</v>
       </c>
       <c r="F94">
-        <v>14837010</v>
+        <v>38590306</v>
       </c>
       <c r="G94">
         <v>7001148</v>
@@ -4230,10 +4230,10 @@
         <v>79092828</v>
       </c>
       <c r="I94">
-        <v>899504</v>
+        <v>3105486</v>
       </c>
       <c r="J94">
-        <v>18363</v>
+        <v>63396</v>
       </c>
       <c r="K94">
         <v>70.8</v>
@@ -4242,7 +4242,7 @@
         <v>1.0411</v>
       </c>
       <c r="M94">
-        <v>552952698</v>
+        <v>1047481379</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -4250,7 +4250,7 @@
         <v>45579</v>
       </c>
       <c r="B95">
-        <v>121142778</v>
+        <v>237383462</v>
       </c>
       <c r="C95">
         <v>8933211</v>
@@ -4259,10 +4259,10 @@
         <v>32</v>
       </c>
       <c r="E95">
-        <v>7182216</v>
+        <v>16500016</v>
       </c>
       <c r="F95">
-        <v>33210700</v>
+        <v>76296381</v>
       </c>
       <c r="G95">
         <v>6705618</v>
@@ -4271,10 +4271,10 @@
         <v>75570169</v>
       </c>
       <c r="I95">
-        <v>2266779</v>
+        <v>7460389</v>
       </c>
       <c r="J95">
-        <v>45957</v>
+        <v>151254</v>
       </c>
       <c r="K95">
         <v>83.8</v>
@@ -4283,7 +4283,7 @@
         <v>1.0342</v>
       </c>
       <c r="M95">
-        <v>554940343</v>
+        <v>1051246657</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -4291,7 +4291,7 @@
         <v>45586</v>
       </c>
       <c r="B96">
-        <v>120848793</v>
+        <v>232390580</v>
       </c>
       <c r="C96">
         <v>7878905</v>
@@ -4300,10 +4300,10 @@
         <v>30.1</v>
       </c>
       <c r="E96">
-        <v>4652492</v>
+        <v>10701554</v>
       </c>
       <c r="F96">
-        <v>20982648</v>
+        <v>48263795</v>
       </c>
       <c r="G96">
         <v>12977941</v>
@@ -4312,10 +4312,10 @@
         <v>144773043</v>
       </c>
       <c r="I96">
-        <v>1604727</v>
+        <v>5352622</v>
       </c>
       <c r="J96">
-        <v>33155</v>
+        <v>110590</v>
       </c>
       <c r="K96">
         <v>89.59999999999999</v>
@@ -4324,7 +4324,7 @@
         <v>0.9781</v>
       </c>
       <c r="M96">
-        <v>596657223</v>
+        <v>1130272684</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -4332,7 +4332,7 @@
         <v>45593</v>
       </c>
       <c r="B97">
-        <v>119231256</v>
+        <v>227592955</v>
       </c>
       <c r="C97">
         <v>185702</v>
@@ -4341,10 +4341,10 @@
         <v>0.7</v>
       </c>
       <c r="E97">
-        <v>3178344</v>
+        <v>8152877</v>
       </c>
       <c r="F97">
-        <v>14716020</v>
+        <v>37748562</v>
       </c>
       <c r="G97">
         <v>9594181</v>
@@ -4353,10 +4353,10 @@
         <v>112950969</v>
       </c>
       <c r="I97">
-        <v>2263160</v>
+        <v>7387772</v>
       </c>
       <c r="J97">
-        <v>43806</v>
+        <v>143000</v>
       </c>
       <c r="K97">
         <v>95</v>
@@ -4365,7 +4365,7 @@
         <v>1.0367</v>
       </c>
       <c r="M97">
-        <v>565168667</v>
+        <v>1070622598</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -4373,7 +4373,7 @@
         <v>45600</v>
       </c>
       <c r="B98">
-        <v>122311554</v>
+        <v>234438479</v>
       </c>
       <c r="C98">
         <v>15008598</v>
@@ -4382,10 +4382,10 @@
         <v>54.3</v>
       </c>
       <c r="E98">
-        <v>3750207</v>
+        <v>9451875</v>
       </c>
       <c r="F98">
-        <v>16324805</v>
+        <v>41144401</v>
       </c>
       <c r="G98">
         <v>10694012</v>
@@ -4394,10 +4394,10 @@
         <v>118633731</v>
       </c>
       <c r="I98">
-        <v>2320323</v>
+        <v>7385793</v>
       </c>
       <c r="J98">
-        <v>49142</v>
+        <v>156423</v>
       </c>
       <c r="K98">
         <v>51.8</v>
@@ -4406,7 +4406,7 @@
         <v>1.0537</v>
       </c>
       <c r="M98">
-        <v>566098176</v>
+        <v>1072383406</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -4414,7 +4414,7 @@
         <v>45607</v>
       </c>
       <c r="B99">
-        <v>123570428</v>
+        <v>237192874</v>
       </c>
       <c r="C99">
         <v>15019086</v>
@@ -4423,10 +4423,10 @@
         <v>53.9</v>
       </c>
       <c r="E99">
-        <v>6100721</v>
+        <v>14168924</v>
       </c>
       <c r="F99">
-        <v>27704508</v>
+        <v>64343713</v>
       </c>
       <c r="G99">
         <v>10642498</v>
@@ -4435,10 +4435,10 @@
         <v>119441936</v>
       </c>
       <c r="I99">
-        <v>1314079</v>
+        <v>4476192</v>
       </c>
       <c r="J99">
-        <v>26838</v>
+        <v>91419</v>
       </c>
       <c r="K99">
         <v>117.8</v>
@@ -4447,7 +4447,7 @@
         <v>1.018</v>
       </c>
       <c r="M99">
-        <v>617828877</v>
+        <v>1170379032</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -4455,7 +4455,7 @@
         <v>45614</v>
       </c>
       <c r="B100">
-        <v>119221674</v>
+        <v>227988835</v>
       </c>
       <c r="C100">
         <v>7503555</v>
@@ -4464,10 +4464,10 @@
         <v>28.1</v>
       </c>
       <c r="E100">
-        <v>3577543</v>
+        <v>8347593</v>
       </c>
       <c r="F100">
-        <v>16401741</v>
+        <v>38270689</v>
       </c>
       <c r="G100">
         <v>3599150</v>
@@ -4476,10 +4476,10 @@
         <v>40872067</v>
       </c>
       <c r="I100">
-        <v>1385871</v>
+        <v>4743921</v>
       </c>
       <c r="J100">
-        <v>27263</v>
+        <v>93324</v>
       </c>
       <c r="K100">
         <v>175.7</v>
@@ -4488,7 +4488,7 @@
         <v>0.9813</v>
       </c>
       <c r="M100">
-        <v>617999898</v>
+        <v>1170703005</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -4496,7 +4496,7 @@
         <v>45621</v>
       </c>
       <c r="B101">
-        <v>121304952</v>
+        <v>233614704</v>
       </c>
       <c r="C101">
         <v>382616</v>
@@ -4505,10 +4505,10 @@
         <v>1.4</v>
       </c>
       <c r="E101">
-        <v>5102592</v>
+        <v>12307081</v>
       </c>
       <c r="F101">
-        <v>22792470</v>
+        <v>54973781</v>
       </c>
       <c r="G101">
         <v>6068500</v>
@@ -4517,10 +4517,10 @@
         <v>72834677</v>
       </c>
       <c r="I101">
-        <v>1612323</v>
+        <v>5338326</v>
       </c>
       <c r="J101">
-        <v>33707</v>
+        <v>111602</v>
       </c>
       <c r="K101">
         <v>129.6</v>
@@ -4529,7 +4529,7 @@
         <v>0.9947</v>
       </c>
       <c r="M101">
-        <v>602463584</v>
+        <v>1141271916</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -4537,7 +4537,7 @@
         <v>45628</v>
       </c>
       <c r="B102">
-        <v>129380983</v>
+        <v>249283705</v>
       </c>
       <c r="C102">
         <v>17946419</v>
@@ -4546,10 +4546,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="E102">
-        <v>4435780</v>
+        <v>10782296</v>
       </c>
       <c r="F102">
-        <v>20980506</v>
+        <v>50998481</v>
       </c>
       <c r="G102">
         <v>11941309</v>
@@ -4558,10 +4558,10 @@
         <v>135472101</v>
       </c>
       <c r="I102">
-        <v>2847943</v>
+        <v>9103112</v>
       </c>
       <c r="J102">
-        <v>55492</v>
+        <v>177373</v>
       </c>
       <c r="K102">
         <v>106.3</v>
@@ -4570,7 +4570,7 @@
         <v>1.0138</v>
       </c>
       <c r="M102">
-        <v>604046617</v>
+        <v>1144270721</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -4578,7 +4578,7 @@
         <v>45635</v>
       </c>
       <c r="B103">
-        <v>126121625</v>
+        <v>229377976</v>
       </c>
       <c r="C103">
         <v>13182173</v>
@@ -4587,10 +4587,10 @@
         <v>48.6</v>
       </c>
       <c r="E103">
-        <v>7364918</v>
+        <v>17663949</v>
       </c>
       <c r="F103">
-        <v>33594369</v>
+        <v>80572414</v>
       </c>
       <c r="G103">
         <v>5999927</v>
@@ -4599,10 +4599,10 @@
         <v>70802944</v>
       </c>
       <c r="I103">
-        <v>198094</v>
+        <v>693328</v>
       </c>
       <c r="J103">
-        <v>4000</v>
+        <v>14000</v>
       </c>
       <c r="K103">
         <v>125</v>
@@ -4611,7 +4611,7 @@
         <v>1.0746</v>
       </c>
       <c r="M103">
-        <v>626794542</v>
+        <v>1187363067</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -4619,7 +4619,7 @@
         <v>45642</v>
       </c>
       <c r="B104">
-        <v>128462633</v>
+        <v>243637067</v>
       </c>
       <c r="C104">
         <v>25069541</v>
@@ -4628,10 +4628,10 @@
         <v>86.5</v>
       </c>
       <c r="E104">
-        <v>5717196</v>
+        <v>13603642</v>
       </c>
       <c r="F104">
-        <v>26687571</v>
+        <v>63501090</v>
       </c>
       <c r="G104">
         <v>4356135</v>
@@ -4640,10 +4640,10 @@
         <v>47532527</v>
       </c>
       <c r="I104">
-        <v>1302078</v>
+        <v>4420666</v>
       </c>
       <c r="J104">
-        <v>26120</v>
+        <v>88678</v>
       </c>
       <c r="K104">
         <v>73.40000000000001</v>
@@ -4652,7 +4652,7 @@
         <v>1.0259</v>
       </c>
       <c r="M104">
-        <v>618443082</v>
+        <v>1171542547</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -4660,7 +4660,7 @@
         <v>45649</v>
       </c>
       <c r="B105">
-        <v>134322021</v>
+        <v>253909685</v>
       </c>
       <c r="C105">
         <v>17684212</v>
@@ -4669,10 +4669,10 @@
         <v>61.3</v>
       </c>
       <c r="E105">
-        <v>7899513</v>
+        <v>18555242</v>
       </c>
       <c r="F105">
-        <v>36717582</v>
+        <v>86246287</v>
       </c>
       <c r="G105">
         <v>6293755</v>
@@ -4681,10 +4681,10 @@
         <v>68672183</v>
       </c>
       <c r="I105">
-        <v>1739217</v>
+        <v>5705198</v>
       </c>
       <c r="J105">
-        <v>33495</v>
+        <v>109873</v>
       </c>
       <c r="K105">
         <v>74.2</v>
@@ -4693,7 +4693,7 @@
         <v>0.9846</v>
       </c>
       <c r="M105">
-        <v>600755452</v>
+        <v>1138036131</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -4707,10 +4707,10 @@
         <v>37.6</v>
       </c>
       <c r="E106">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F106">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G106">
         <v>7237098</v>
@@ -4719,10 +4719,10 @@
         <v>83779662</v>
       </c>
       <c r="I106">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J106">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -4736,10 +4736,10 @@
         <v>37.6</v>
       </c>
       <c r="E107">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F107">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G107">
         <v>7237098</v>
@@ -4748,10 +4748,10 @@
         <v>83779662</v>
       </c>
       <c r="I107">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J107">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -4765,10 +4765,10 @@
         <v>37.6</v>
       </c>
       <c r="E108">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F108">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G108">
         <v>7237098</v>
@@ -4777,10 +4777,10 @@
         <v>83779662</v>
       </c>
       <c r="I108">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J108">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -4794,10 +4794,10 @@
         <v>37.6</v>
       </c>
       <c r="E109">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F109">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G109">
         <v>7237098</v>
@@ -4806,10 +4806,10 @@
         <v>83779662</v>
       </c>
       <c r="I109">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J109">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -4823,10 +4823,10 @@
         <v>37.6</v>
       </c>
       <c r="E110">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F110">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G110">
         <v>7237098</v>
@@ -4835,10 +4835,10 @@
         <v>83779662</v>
       </c>
       <c r="I110">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J110">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -4852,10 +4852,10 @@
         <v>37.6</v>
       </c>
       <c r="E111">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F111">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G111">
         <v>7237098</v>
@@ -4864,10 +4864,10 @@
         <v>83779662</v>
       </c>
       <c r="I111">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J111">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -4881,10 +4881,10 @@
         <v>37.6</v>
       </c>
       <c r="E112">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F112">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G112">
         <v>7237098</v>
@@ -4893,10 +4893,10 @@
         <v>83779662</v>
       </c>
       <c r="I112">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J112">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -4910,10 +4910,10 @@
         <v>37.6</v>
       </c>
       <c r="E113">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F113">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G113">
         <v>7237098</v>
@@ -4922,10 +4922,10 @@
         <v>83779662</v>
       </c>
       <c r="I113">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J113">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -4939,10 +4939,10 @@
         <v>37.6</v>
       </c>
       <c r="E114">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F114">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G114">
         <v>7237098</v>
@@ -4951,10 +4951,10 @@
         <v>83779662</v>
       </c>
       <c r="I114">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J114">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -4968,10 +4968,10 @@
         <v>37.6</v>
       </c>
       <c r="E115">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F115">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G115">
         <v>7237098</v>
@@ -4980,10 +4980,10 @@
         <v>83779662</v>
       </c>
       <c r="I115">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J115">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -4997,10 +4997,10 @@
         <v>37.6</v>
       </c>
       <c r="E116">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F116">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G116">
         <v>7237098</v>
@@ -5009,10 +5009,10 @@
         <v>83779662</v>
       </c>
       <c r="I116">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J116">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -5026,10 +5026,10 @@
         <v>37.6</v>
       </c>
       <c r="E117">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F117">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G117">
         <v>7237098</v>
@@ -5038,10 +5038,10 @@
         <v>83779662</v>
       </c>
       <c r="I117">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J117">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -5055,10 +5055,10 @@
         <v>37.6</v>
       </c>
       <c r="E118">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F118">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G118">
         <v>7237098</v>
@@ -5067,10 +5067,10 @@
         <v>83779662</v>
       </c>
       <c r="I118">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J118">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -5084,10 +5084,10 @@
         <v>37.6</v>
       </c>
       <c r="E119">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F119">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G119">
         <v>7237098</v>
@@ -5096,10 +5096,10 @@
         <v>83779662</v>
       </c>
       <c r="I119">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J119">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -5113,10 +5113,10 @@
         <v>37.6</v>
       </c>
       <c r="E120">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F120">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G120">
         <v>7237098</v>
@@ -5125,10 +5125,10 @@
         <v>83779662</v>
       </c>
       <c r="I120">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J120">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -5142,10 +5142,10 @@
         <v>37.6</v>
       </c>
       <c r="E121">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F121">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G121">
         <v>7237098</v>
@@ -5154,10 +5154,10 @@
         <v>83779662</v>
       </c>
       <c r="I121">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J121">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="122" spans="1:10">
@@ -5171,10 +5171,10 @@
         <v>37.6</v>
       </c>
       <c r="E122">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F122">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G122">
         <v>7237098</v>
@@ -5183,10 +5183,10 @@
         <v>83779662</v>
       </c>
       <c r="I122">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J122">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -5200,10 +5200,10 @@
         <v>37.6</v>
       </c>
       <c r="E123">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F123">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G123">
         <v>7237098</v>
@@ -5212,10 +5212,10 @@
         <v>83779662</v>
       </c>
       <c r="I123">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J123">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -5229,10 +5229,10 @@
         <v>37.6</v>
       </c>
       <c r="E124">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F124">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G124">
         <v>7237098</v>
@@ -5241,10 +5241,10 @@
         <v>83779662</v>
       </c>
       <c r="I124">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J124">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -5258,10 +5258,10 @@
         <v>37.6</v>
       </c>
       <c r="E125">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F125">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G125">
         <v>7237098</v>
@@ -5270,10 +5270,10 @@
         <v>83779662</v>
       </c>
       <c r="I125">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J125">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -5287,10 +5287,10 @@
         <v>37.6</v>
       </c>
       <c r="E126">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F126">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G126">
         <v>7237098</v>
@@ -5299,10 +5299,10 @@
         <v>83779662</v>
       </c>
       <c r="I126">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J126">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -5316,10 +5316,10 @@
         <v>37.6</v>
       </c>
       <c r="E127">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F127">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G127">
         <v>7237098</v>
@@ -5328,10 +5328,10 @@
         <v>83779662</v>
       </c>
       <c r="I127">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J127">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -5345,10 +5345,10 @@
         <v>37.6</v>
       </c>
       <c r="E128">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F128">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G128">
         <v>7237098</v>
@@ -5357,10 +5357,10 @@
         <v>83779662</v>
       </c>
       <c r="I128">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J128">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -5374,10 +5374,10 @@
         <v>37.6</v>
       </c>
       <c r="E129">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F129">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G129">
         <v>7237098</v>
@@ -5386,10 +5386,10 @@
         <v>83779662</v>
       </c>
       <c r="I129">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J129">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -5403,10 +5403,10 @@
         <v>37.6</v>
       </c>
       <c r="E130">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F130">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G130">
         <v>7237098</v>
@@ -5415,10 +5415,10 @@
         <v>83779662</v>
       </c>
       <c r="I130">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J130">
-        <v>35265</v>
+        <v>115337</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -5432,10 +5432,10 @@
         <v>37.6</v>
       </c>
       <c r="E131">
-        <v>5030271</v>
+        <v>12036018</v>
       </c>
       <c r="F131">
-        <v>23333170</v>
+        <v>55829685</v>
       </c>
       <c r="G131">
         <v>7237098</v>
@@ -5444,10 +5444,184 @@
         <v>83779662</v>
       </c>
       <c r="I131">
-        <v>1723157</v>
+        <v>5635748</v>
       </c>
       <c r="J131">
-        <v>35265</v>
+        <v>115337</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" s="1">
+        <v>45838</v>
+      </c>
+      <c r="C132">
+        <v>10151647</v>
+      </c>
+      <c r="D132">
+        <v>37.6</v>
+      </c>
+      <c r="E132">
+        <v>12036018</v>
+      </c>
+      <c r="F132">
+        <v>55829685</v>
+      </c>
+      <c r="G132">
+        <v>7237098</v>
+      </c>
+      <c r="H132">
+        <v>83779662</v>
+      </c>
+      <c r="I132">
+        <v>5635748</v>
+      </c>
+      <c r="J132">
+        <v>115337</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" s="1">
+        <v>45845</v>
+      </c>
+      <c r="C133">
+        <v>10151647</v>
+      </c>
+      <c r="D133">
+        <v>37.6</v>
+      </c>
+      <c r="E133">
+        <v>12036018</v>
+      </c>
+      <c r="F133">
+        <v>55829685</v>
+      </c>
+      <c r="G133">
+        <v>7237098</v>
+      </c>
+      <c r="H133">
+        <v>83779662</v>
+      </c>
+      <c r="I133">
+        <v>5635748</v>
+      </c>
+      <c r="J133">
+        <v>115337</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" s="1">
+        <v>45852</v>
+      </c>
+      <c r="C134">
+        <v>10151647</v>
+      </c>
+      <c r="D134">
+        <v>37.6</v>
+      </c>
+      <c r="E134">
+        <v>12036018</v>
+      </c>
+      <c r="F134">
+        <v>55829685</v>
+      </c>
+      <c r="G134">
+        <v>7237098</v>
+      </c>
+      <c r="H134">
+        <v>83779662</v>
+      </c>
+      <c r="I134">
+        <v>5635748</v>
+      </c>
+      <c r="J134">
+        <v>115337</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" s="1">
+        <v>45859</v>
+      </c>
+      <c r="C135">
+        <v>10151647</v>
+      </c>
+      <c r="D135">
+        <v>37.6</v>
+      </c>
+      <c r="E135">
+        <v>12036018</v>
+      </c>
+      <c r="F135">
+        <v>55829685</v>
+      </c>
+      <c r="G135">
+        <v>7237098</v>
+      </c>
+      <c r="H135">
+        <v>83779662</v>
+      </c>
+      <c r="I135">
+        <v>5635748</v>
+      </c>
+      <c r="J135">
+        <v>115337</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136" s="1">
+        <v>45866</v>
+      </c>
+      <c r="C136">
+        <v>10151647</v>
+      </c>
+      <c r="D136">
+        <v>37.6</v>
+      </c>
+      <c r="E136">
+        <v>12036018</v>
+      </c>
+      <c r="F136">
+        <v>55829685</v>
+      </c>
+      <c r="G136">
+        <v>7237098</v>
+      </c>
+      <c r="H136">
+        <v>83779662</v>
+      </c>
+      <c r="I136">
+        <v>5635748</v>
+      </c>
+      <c r="J136">
+        <v>115337</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137" s="1">
+        <v>45873</v>
+      </c>
+      <c r="C137">
+        <v>10151647</v>
+      </c>
+      <c r="D137">
+        <v>37.6</v>
+      </c>
+      <c r="E137">
+        <v>12036018</v>
+      </c>
+      <c r="F137">
+        <v>55829685</v>
+      </c>
+      <c r="G137">
+        <v>7237098</v>
+      </c>
+      <c r="H137">
+        <v>83779662</v>
+      </c>
+      <c r="I137">
+        <v>5635748</v>
+      </c>
+      <c r="J137">
+        <v>115337</v>
       </c>
     </row>
   </sheetData>
